--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W380"/>
+  <dimension ref="A1:W381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28966,6 +28966,81 @@
         <v>363.13</v>
       </c>
       <c r="W380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="C381" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="D381" t="n">
+        <v>369.7</v>
+      </c>
+      <c r="E381" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="F381" t="n">
+        <v>397.24</v>
+      </c>
+      <c r="G381" t="n">
+        <v>411.38</v>
+      </c>
+      <c r="H381" t="n">
+        <v>410.08</v>
+      </c>
+      <c r="I381" t="n">
+        <v>399.53</v>
+      </c>
+      <c r="J381" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="K381" t="n">
+        <v>377.42</v>
+      </c>
+      <c r="L381" t="n">
+        <v>384.51</v>
+      </c>
+      <c r="M381" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="N381" t="n">
+        <v>371.48</v>
+      </c>
+      <c r="O381" t="n">
+        <v>365.09</v>
+      </c>
+      <c r="P381" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="R381" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="S381" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="T381" t="n">
+        <v>365.48</v>
+      </c>
+      <c r="U381" t="n">
+        <v>361.45</v>
+      </c>
+      <c r="V381" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="W381" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28982,7 +29057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B390"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32885,6 +32960,16 @@
       </c>
       <c r="B390" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -33053,28 +33138,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2064854484017266</v>
+        <v>-0.2086859557364463</v>
       </c>
       <c r="J2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K2" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09782376916500868</v>
+        <v>0.1000892503177799</v>
       </c>
       <c r="M2" t="n">
-        <v>3.703636712268859</v>
+        <v>3.70353974618163</v>
       </c>
       <c r="N2" t="n">
-        <v>19.48299105370287</v>
+        <v>19.47044380409946</v>
       </c>
       <c r="O2" t="n">
-        <v>4.413954129089118</v>
+        <v>4.412532583913626</v>
       </c>
       <c r="P2" t="n">
-        <v>401.5798366145673</v>
+        <v>401.6036905468372</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33131,28 +33216,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009767202974396297</v>
+        <v>0.005675269847741805</v>
       </c>
       <c r="J3" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K3" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001411173986667347</v>
+        <v>4.775383841026937e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.628918797525256</v>
+        <v>4.636203905210447</v>
       </c>
       <c r="N3" t="n">
-        <v>33.49101527085222</v>
+        <v>33.53678366411137</v>
       </c>
       <c r="O3" t="n">
-        <v>5.78714223696396</v>
+        <v>5.79109520420027</v>
       </c>
       <c r="P3" t="n">
-        <v>381.0347714555667</v>
+        <v>381.0791288153974</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33209,28 +33294,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1536891366601675</v>
+        <v>0.1509880545144286</v>
       </c>
       <c r="J4" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K4" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03299839463320198</v>
+        <v>0.03202438338703562</v>
       </c>
       <c r="M4" t="n">
-        <v>4.558853048751526</v>
+        <v>4.55930495241446</v>
       </c>
       <c r="N4" t="n">
-        <v>34.29655237831093</v>
+        <v>34.26464383553995</v>
       </c>
       <c r="O4" t="n">
-        <v>5.8563258429079</v>
+        <v>5.853600928961587</v>
       </c>
       <c r="P4" t="n">
-        <v>370.3924637125456</v>
+        <v>370.4217439742123</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -33291,28 +33376,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2109721444553461</v>
+        <v>0.2087214661127063</v>
       </c>
       <c r="J5" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K5" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09075074896531177</v>
+        <v>0.08935049929335159</v>
       </c>
       <c r="M5" t="n">
-        <v>3.575363795267604</v>
+        <v>3.576624043968263</v>
       </c>
       <c r="N5" t="n">
-        <v>22.09595155273105</v>
+        <v>22.07831400566818</v>
       </c>
       <c r="O5" t="n">
-        <v>4.700633101267429</v>
+        <v>4.69875664465273</v>
       </c>
       <c r="P5" t="n">
-        <v>381.5337796434578</v>
+        <v>381.5581774393204</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33369,28 +33454,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1531370322724929</v>
+        <v>0.1495133665389362</v>
       </c>
       <c r="J6" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K6" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08059469402956176</v>
+        <v>0.07699445333155008</v>
       </c>
       <c r="M6" t="n">
-        <v>3.01000991092057</v>
+        <v>3.018261947823558</v>
       </c>
       <c r="N6" t="n">
-        <v>13.25533621879222</v>
+        <v>13.32546319827184</v>
       </c>
       <c r="O6" t="n">
-        <v>3.640787856878264</v>
+        <v>3.650405895002889</v>
       </c>
       <c r="P6" t="n">
-        <v>399.5641427668161</v>
+        <v>399.6034240160142</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33447,28 +33532,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06509960604877271</v>
+        <v>0.06125083826846584</v>
       </c>
       <c r="J7" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K7" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0117120516321918</v>
+        <v>0.01037712744326458</v>
       </c>
       <c r="M7" t="n">
-        <v>3.370655690439891</v>
+        <v>3.382127751317032</v>
       </c>
       <c r="N7" t="n">
-        <v>17.71890918592913</v>
+        <v>17.79074151011159</v>
       </c>
       <c r="O7" t="n">
-        <v>4.209383468624488</v>
+        <v>4.217907242947809</v>
       </c>
       <c r="P7" t="n">
-        <v>416.4083507998981</v>
+        <v>416.4500721995525</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33525,28 +33610,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01194605446437337</v>
+        <v>-0.01714449170278729</v>
       </c>
       <c r="J8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003306057501734072</v>
+        <v>0.0006780669347100643</v>
       </c>
       <c r="M8" t="n">
-        <v>3.641678263962797</v>
+        <v>3.657317341711543</v>
       </c>
       <c r="N8" t="n">
-        <v>21.3808375732991</v>
+        <v>21.54068362651992</v>
       </c>
       <c r="O8" t="n">
-        <v>4.623941778753178</v>
+        <v>4.64119420262931</v>
       </c>
       <c r="P8" t="n">
-        <v>419.4919615435819</v>
+        <v>419.548313625594</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33603,28 +33688,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09824417246391903</v>
+        <v>-0.1017165946497731</v>
       </c>
       <c r="J9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02317401755709669</v>
+        <v>0.02483400922748735</v>
       </c>
       <c r="M9" t="n">
-        <v>3.562635456268426</v>
+        <v>3.568113921116402</v>
       </c>
       <c r="N9" t="n">
-        <v>20.1585462356314</v>
+        <v>20.20192409374109</v>
       </c>
       <c r="O9" t="n">
-        <v>4.48982697168069</v>
+        <v>4.49465505837112</v>
       </c>
       <c r="P9" t="n">
-        <v>408.1917041554792</v>
+        <v>408.2293458948758</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33681,28 +33766,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09879520037018059</v>
+        <v>-0.1024853974834201</v>
       </c>
       <c r="J10" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K10" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02366345622846522</v>
+        <v>0.02543682755238852</v>
       </c>
       <c r="M10" t="n">
-        <v>3.585643304073344</v>
+        <v>3.595024211607586</v>
       </c>
       <c r="N10" t="n">
-        <v>19.95367071986208</v>
+        <v>20.01006189938333</v>
       </c>
       <c r="O10" t="n">
-        <v>4.466953180845091</v>
+        <v>4.473260768095611</v>
       </c>
       <c r="P10" t="n">
-        <v>396.7487279324758</v>
+        <v>396.788730394914</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33759,28 +33844,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1673867922537947</v>
+        <v>-0.1726920006953183</v>
       </c>
       <c r="J11" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K11" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06600801944385748</v>
+        <v>0.0696219501003561</v>
       </c>
       <c r="M11" t="n">
-        <v>3.548484522892024</v>
+        <v>3.564680674146221</v>
       </c>
       <c r="N11" t="n">
-        <v>19.64348588286929</v>
+        <v>19.81687254813493</v>
       </c>
       <c r="O11" t="n">
-        <v>4.432097233011624</v>
+        <v>4.451614600134981</v>
       </c>
       <c r="P11" t="n">
-        <v>391.1056461624906</v>
+        <v>391.1631556653427</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33837,28 +33922,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1652557731392216</v>
+        <v>-0.1650103602901266</v>
       </c>
       <c r="J12" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K12" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06034312723661095</v>
+        <v>0.0605250246482012</v>
       </c>
       <c r="M12" t="n">
-        <v>3.722443563990816</v>
+        <v>3.713881479187447</v>
       </c>
       <c r="N12" t="n">
-        <v>21.07096870554421</v>
+        <v>21.01600043249424</v>
       </c>
       <c r="O12" t="n">
-        <v>4.590312484520439</v>
+        <v>4.584321152852867</v>
       </c>
       <c r="P12" t="n">
-        <v>388.4165311722164</v>
+        <v>388.4138708486683</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33915,28 +34000,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1838586541274196</v>
+        <v>-0.1895031565980105</v>
       </c>
       <c r="J13" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K13" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0446707276092827</v>
+        <v>0.04728292847193738</v>
       </c>
       <c r="M13" t="n">
-        <v>4.74907922404499</v>
+        <v>4.758044980216912</v>
       </c>
       <c r="N13" t="n">
-        <v>35.82019555273258</v>
+        <v>35.98072249828451</v>
       </c>
       <c r="O13" t="n">
-        <v>5.98499753991032</v>
+        <v>5.998393326407039</v>
       </c>
       <c r="P13" t="n">
-        <v>389.2890935134644</v>
+        <v>389.3502810303186</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33993,28 +34078,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1594952470343523</v>
+        <v>-0.1659449128771554</v>
       </c>
       <c r="J14" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K14" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03013710767321243</v>
+        <v>0.03248022504712278</v>
       </c>
       <c r="M14" t="n">
-        <v>4.955307235598577</v>
+        <v>4.976795496475448</v>
       </c>
       <c r="N14" t="n">
-        <v>40.56336775583081</v>
+        <v>40.78928660346514</v>
       </c>
       <c r="O14" t="n">
-        <v>6.368937725855923</v>
+        <v>6.386649090365396</v>
       </c>
       <c r="P14" t="n">
-        <v>386.9631881503241</v>
+        <v>387.03310379648</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34071,28 +34156,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2141164910049592</v>
+        <v>-0.2195130114356748</v>
       </c>
       <c r="J15" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K15" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05191304539250208</v>
+        <v>0.05444877564720818</v>
       </c>
       <c r="M15" t="n">
-        <v>4.997198937949183</v>
+        <v>5.014230676096573</v>
       </c>
       <c r="N15" t="n">
-        <v>41.48600728056883</v>
+        <v>41.60972835398143</v>
       </c>
       <c r="O15" t="n">
-        <v>6.440963226146291</v>
+        <v>6.450560313180665</v>
       </c>
       <c r="P15" t="n">
-        <v>380.1590775214565</v>
+        <v>380.2175768642292</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34149,28 +34234,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1320316461840089</v>
+        <v>-0.1389551293500847</v>
       </c>
       <c r="J16" t="n">
+        <v>380</v>
+      </c>
+      <c r="K16" t="n">
         <v>379</v>
       </c>
-      <c r="K16" t="n">
-        <v>378</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02033737468565644</v>
+        <v>0.02241280635625142</v>
       </c>
       <c r="M16" t="n">
-        <v>4.999975256266487</v>
+        <v>5.023169987303382</v>
       </c>
       <c r="N16" t="n">
-        <v>41.64227484541328</v>
+        <v>41.91430084039416</v>
       </c>
       <c r="O16" t="n">
-        <v>6.453082584735243</v>
+        <v>6.474125488465154</v>
       </c>
       <c r="P16" t="n">
-        <v>375.4270559576397</v>
+        <v>375.502019788686</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34227,28 +34312,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1082935612281035</v>
+        <v>-0.1135211307062384</v>
       </c>
       <c r="J17" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K17" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01380469809886964</v>
+        <v>0.0151628979934777</v>
       </c>
       <c r="M17" t="n">
-        <v>4.991067456651749</v>
+        <v>5.002378055377123</v>
       </c>
       <c r="N17" t="n">
-        <v>41.51174860994496</v>
+        <v>41.62104756167969</v>
       </c>
       <c r="O17" t="n">
-        <v>6.442961167812899</v>
+        <v>6.451437635262367</v>
       </c>
       <c r="P17" t="n">
-        <v>369.3948372830815</v>
+        <v>369.4515051643016</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34305,28 +34390,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1196031914988433</v>
+        <v>-0.1214809473704147</v>
       </c>
       <c r="J18" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K18" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0252565364465942</v>
+        <v>0.02616631010457626</v>
       </c>
       <c r="M18" t="n">
-        <v>4.18866645704154</v>
+        <v>4.186296782815323</v>
       </c>
       <c r="N18" t="n">
-        <v>27.35469114231029</v>
+        <v>27.31090259671405</v>
       </c>
       <c r="O18" t="n">
-        <v>5.23017123451138</v>
+        <v>5.22598340953299</v>
       </c>
       <c r="P18" t="n">
-        <v>364.7976381308333</v>
+        <v>364.8179933737689</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34383,28 +34468,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1268880097762885</v>
+        <v>-0.1284656560632066</v>
       </c>
       <c r="J19" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K19" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02287234623369594</v>
+        <v>0.02356002146471481</v>
       </c>
       <c r="M19" t="n">
-        <v>4.536675593639801</v>
+        <v>4.532487559007614</v>
       </c>
       <c r="N19" t="n">
-        <v>34.08093486664885</v>
+        <v>34.01115270071629</v>
       </c>
       <c r="O19" t="n">
-        <v>5.83788787719059</v>
+        <v>5.831908152630346</v>
       </c>
       <c r="P19" t="n">
-        <v>366.5333088868753</v>
+        <v>366.5504108828924</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34461,28 +34546,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1362304805070653</v>
+        <v>-0.1386640969837769</v>
       </c>
       <c r="J20" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K20" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02303787211787256</v>
+        <v>0.02396476134133874</v>
       </c>
       <c r="M20" t="n">
-        <v>5.059248928400991</v>
+        <v>5.057030704730954</v>
       </c>
       <c r="N20" t="n">
-        <v>38.9954272056594</v>
+        <v>38.94017035158669</v>
       </c>
       <c r="O20" t="n">
-        <v>6.244631871108128</v>
+        <v>6.240205954260379</v>
       </c>
       <c r="P20" t="n">
-        <v>373.3172202366739</v>
+        <v>373.3436011178872</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34539,28 +34624,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.125883660351275</v>
+        <v>-0.1267717919855496</v>
       </c>
       <c r="J21" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K21" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02365865922868904</v>
+        <v>0.02412657984436239</v>
       </c>
       <c r="M21" t="n">
-        <v>4.551795938995775</v>
+        <v>4.543404010762731</v>
       </c>
       <c r="N21" t="n">
-        <v>32.40261161416002</v>
+        <v>32.32364951230331</v>
       </c>
       <c r="O21" t="n">
-        <v>5.692329190600279</v>
+        <v>5.685389125847352</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3067859244741</v>
+        <v>366.3164134460536</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34617,28 +34702,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1219113770050411</v>
+        <v>-0.1214082805402186</v>
       </c>
       <c r="J22" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K22" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02308713662762252</v>
+        <v>0.02303898730346166</v>
       </c>
       <c r="M22" t="n">
-        <v>4.464494250099642</v>
+        <v>4.455140304819031</v>
       </c>
       <c r="N22" t="n">
-        <v>31.16046778869255</v>
+        <v>31.08049067008447</v>
       </c>
       <c r="O22" t="n">
-        <v>5.582156195296989</v>
+        <v>5.574987952460926</v>
       </c>
       <c r="P22" t="n">
-        <v>366.0751425248107</v>
+        <v>366.0696888601908</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34676,7 +34761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W380"/>
+  <dimension ref="A1:W381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79135,6 +79220,123 @@
         </is>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-37.61817667757799,177.9440899625191</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-37.618141744363584,177.94501736416845</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-37.61798892366757,177.94589788231323</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-37.61768297931232,177.94671749995186</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-37.61737120507438,177.9475347975993</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-37.617068155395835,177.94832315206827</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-37.61685560812046,177.94907236651835</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-37.61656641042819,177.94983885731625</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>-37.61625809259967,177.95066435955317</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>-37.61593845434782,177.9514796350378</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>-37.61549198436254,177.95218030165108</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>-37.615177346329666,177.9529841516257</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>-37.61473711572924,177.95366169272856</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>-37.614263636856776,177.95433174683308</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>-37.61377975611022,177.95499524392343</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>-37.613254419892854,177.95560109872656</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>-37.61268030263372,177.95613203830177</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>-37.61210062324602,177.95665192536447</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>-37.611507058188245,177.95712786991845</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>-37.61087322718475,177.9575232925016</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>-37.610211638963285,177.9578528251465</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W381"/>
+  <dimension ref="A1:W382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29043,6 +29043,81 @@
       <c r="W381" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>393.04</v>
+      </c>
+      <c r="C382" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="D382" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="E382" t="n">
+        <v>382.77</v>
+      </c>
+      <c r="F382" t="n">
+        <v>396.89</v>
+      </c>
+      <c r="G382" t="n">
+        <v>410.57</v>
+      </c>
+      <c r="H382" t="n">
+        <v>408.44</v>
+      </c>
+      <c r="I382" t="n">
+        <v>397.24</v>
+      </c>
+      <c r="J382" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="K382" t="n">
+        <v>375.51</v>
+      </c>
+      <c r="L382" t="n">
+        <v>380.33</v>
+      </c>
+      <c r="M382" t="n">
+        <v>366.56</v>
+      </c>
+      <c r="N382" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="O382" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="P382" t="n">
+        <v>359.47</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="R382" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="S382" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="T382" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="U382" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="V382" t="n">
+        <v>364.31</v>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29057,7 +29132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32970,6 +33045,16 @@
       </c>
       <c r="B391" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -33138,28 +33223,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2086859557364463</v>
+        <v>-0.2104353865138127</v>
       </c>
       <c r="J2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1000892503177799</v>
+        <v>0.1020549604215699</v>
       </c>
       <c r="M2" t="n">
-        <v>3.70353974618163</v>
+        <v>3.701541275113587</v>
       </c>
       <c r="N2" t="n">
-        <v>19.47044380409946</v>
+        <v>19.44388641936075</v>
       </c>
       <c r="O2" t="n">
-        <v>4.412532583913626</v>
+        <v>4.409522243890005</v>
       </c>
       <c r="P2" t="n">
-        <v>401.6036905468372</v>
+        <v>401.6227035058139</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33216,28 +33301,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005675269847741805</v>
+        <v>0.002276722580527053</v>
       </c>
       <c r="J3" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K3" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L3" t="n">
-        <v>4.775383841026937e-05</v>
+        <v>7.711975524404835e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>4.636203905210447</v>
+        <v>4.640111403672428</v>
       </c>
       <c r="N3" t="n">
-        <v>33.53678366411137</v>
+        <v>33.54139587552681</v>
       </c>
       <c r="O3" t="n">
-        <v>5.79109520420027</v>
+        <v>5.791493406326801</v>
       </c>
       <c r="P3" t="n">
-        <v>381.0791288153974</v>
+        <v>381.1160645093432</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33294,28 +33379,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1509880545144286</v>
+        <v>0.147867097424045</v>
       </c>
       <c r="J4" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K4" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03202438338703562</v>
+        <v>0.03087151054189852</v>
       </c>
       <c r="M4" t="n">
-        <v>4.55930495241446</v>
+        <v>4.561600483255908</v>
       </c>
       <c r="N4" t="n">
-        <v>34.26464383553995</v>
+        <v>34.25283094171469</v>
       </c>
       <c r="O4" t="n">
-        <v>5.853600928961587</v>
+        <v>5.852591814035444</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4217439742123</v>
+        <v>370.4556627950626</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -33376,28 +33461,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2087214661127063</v>
+        <v>0.2062838862455886</v>
       </c>
       <c r="J5" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K5" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08935049929335159</v>
+        <v>0.08778020964930333</v>
       </c>
       <c r="M5" t="n">
-        <v>3.576624043968263</v>
+        <v>3.578693541644987</v>
       </c>
       <c r="N5" t="n">
-        <v>22.07831400566818</v>
+        <v>22.06802056048243</v>
       </c>
       <c r="O5" t="n">
-        <v>4.69875664465273</v>
+        <v>4.697661179830068</v>
       </c>
       <c r="P5" t="n">
-        <v>381.5581774393204</v>
+        <v>381.5846692597545</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33454,28 +33539,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1495133665389362</v>
+        <v>0.1457265373869898</v>
       </c>
       <c r="J6" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K6" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07699445333155008</v>
+        <v>0.07326237201551433</v>
       </c>
       <c r="M6" t="n">
-        <v>3.018261947823558</v>
+        <v>3.027310638994447</v>
       </c>
       <c r="N6" t="n">
-        <v>13.32546319827184</v>
+        <v>13.40549969699011</v>
       </c>
       <c r="O6" t="n">
-        <v>3.650405895002889</v>
+        <v>3.661352167845933</v>
       </c>
       <c r="P6" t="n">
-        <v>399.6034240160142</v>
+        <v>399.6445795897293</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33532,28 +33617,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06125083826846584</v>
+        <v>0.05698637575815432</v>
       </c>
       <c r="J7" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K7" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01037712744326458</v>
+        <v>0.008977339017389285</v>
       </c>
       <c r="M7" t="n">
-        <v>3.382127751317032</v>
+        <v>3.395831835692029</v>
       </c>
       <c r="N7" t="n">
-        <v>17.79074151011159</v>
+        <v>17.88990064374842</v>
       </c>
       <c r="O7" t="n">
-        <v>4.217907242947809</v>
+        <v>4.229645451305394</v>
       </c>
       <c r="P7" t="n">
-        <v>416.4500721995525</v>
+        <v>416.4964187322734</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33610,28 +33695,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01714449170278729</v>
+        <v>-0.02321356270513545</v>
       </c>
       <c r="J8" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K8" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006780669347100643</v>
+        <v>0.001233185599942455</v>
       </c>
       <c r="M8" t="n">
-        <v>3.657317341711543</v>
+        <v>3.677236733984355</v>
       </c>
       <c r="N8" t="n">
-        <v>21.54068362651992</v>
+        <v>21.77956249819383</v>
       </c>
       <c r="O8" t="n">
-        <v>4.64119420262931</v>
+        <v>4.666857882793714</v>
       </c>
       <c r="P8" t="n">
-        <v>419.548313625594</v>
+        <v>419.6142727932772</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33688,28 +33773,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1017165946497731</v>
+        <v>-0.106450855227054</v>
       </c>
       <c r="J9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02483400922748735</v>
+        <v>0.02706471044789704</v>
       </c>
       <c r="M9" t="n">
-        <v>3.568113921116402</v>
+        <v>3.579020523887274</v>
       </c>
       <c r="N9" t="n">
-        <v>20.20192409374109</v>
+        <v>20.3286610762177</v>
       </c>
       <c r="O9" t="n">
-        <v>4.49465505837112</v>
+        <v>4.508731648281776</v>
       </c>
       <c r="P9" t="n">
-        <v>408.2293458948758</v>
+        <v>408.2807982320047</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33766,28 +33851,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1024853974834201</v>
+        <v>-0.1070362151180871</v>
       </c>
       <c r="J10" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K10" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02543682755238852</v>
+        <v>0.02762600848842922</v>
       </c>
       <c r="M10" t="n">
-        <v>3.595024211607586</v>
+        <v>3.608642141555983</v>
       </c>
       <c r="N10" t="n">
-        <v>20.01006189938333</v>
+        <v>20.12364165202064</v>
       </c>
       <c r="O10" t="n">
-        <v>4.473260768095611</v>
+        <v>4.485938213130074</v>
       </c>
       <c r="P10" t="n">
-        <v>396.788730394914</v>
+        <v>396.8381890589078</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33844,28 +33929,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1726920006953183</v>
+        <v>-0.1790198556338802</v>
       </c>
       <c r="J11" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K11" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0696219501003561</v>
+        <v>0.0737507722057269</v>
       </c>
       <c r="M11" t="n">
-        <v>3.564680674146221</v>
+        <v>3.585886436601935</v>
       </c>
       <c r="N11" t="n">
-        <v>19.81687254813493</v>
+        <v>20.08600593281893</v>
       </c>
       <c r="O11" t="n">
-        <v>4.451614600134981</v>
+        <v>4.48174139512968</v>
       </c>
       <c r="P11" t="n">
-        <v>391.1631556653427</v>
+        <v>391.2319273183363</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33922,28 +34007,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1650103602901266</v>
+        <v>-0.1671444184498415</v>
       </c>
       <c r="J12" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K12" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0605250246482012</v>
+        <v>0.06226297796348279</v>
       </c>
       <c r="M12" t="n">
-        <v>3.713881479187447</v>
+        <v>3.712989113232994</v>
       </c>
       <c r="N12" t="n">
-        <v>21.01600043249424</v>
+        <v>20.99736633560376</v>
       </c>
       <c r="O12" t="n">
-        <v>4.584321152852867</v>
+        <v>4.58228832960168</v>
       </c>
       <c r="P12" t="n">
-        <v>388.4138708486683</v>
+        <v>388.4370639699792</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34000,28 +34085,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1895031565980105</v>
+        <v>-0.1996456610376267</v>
       </c>
       <c r="J13" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K13" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04728292847193738</v>
+        <v>0.05139657297702749</v>
       </c>
       <c r="M13" t="n">
-        <v>4.758044980216912</v>
+        <v>4.783954143461603</v>
       </c>
       <c r="N13" t="n">
-        <v>35.98072249828451</v>
+        <v>36.71133465303591</v>
       </c>
       <c r="O13" t="n">
-        <v>5.998393326407039</v>
+        <v>6.058987923163068</v>
       </c>
       <c r="P13" t="n">
-        <v>389.3502810303186</v>
+        <v>389.460510610892</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34078,28 +34163,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1659449128771554</v>
+        <v>-0.1727171745647075</v>
       </c>
       <c r="J14" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K14" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03248022504712278</v>
+        <v>0.034995827663719</v>
       </c>
       <c r="M14" t="n">
-        <v>4.976795496475448</v>
+        <v>5.000418829621645</v>
       </c>
       <c r="N14" t="n">
-        <v>40.78928660346514</v>
+        <v>41.05006661022907</v>
       </c>
       <c r="O14" t="n">
-        <v>6.386649090365396</v>
+        <v>6.407032590070779</v>
       </c>
       <c r="P14" t="n">
-        <v>387.03310379648</v>
+        <v>387.1067052989291</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34156,28 +34241,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2195130114356748</v>
+        <v>-0.2251557469823451</v>
       </c>
       <c r="J15" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K15" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05444877564720818</v>
+        <v>0.05712576544913106</v>
       </c>
       <c r="M15" t="n">
-        <v>5.014230676096573</v>
+        <v>5.032699068868033</v>
       </c>
       <c r="N15" t="n">
-        <v>41.60972835398143</v>
+        <v>41.75588602157811</v>
       </c>
       <c r="O15" t="n">
-        <v>6.450560313180665</v>
+        <v>6.461879449632135</v>
       </c>
       <c r="P15" t="n">
-        <v>380.2175768642292</v>
+        <v>380.2789025827734</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34234,28 +34319,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1389551293500847</v>
+        <v>-0.1460247039232168</v>
       </c>
       <c r="J16" t="n">
+        <v>381</v>
+      </c>
+      <c r="K16" t="n">
         <v>380</v>
       </c>
-      <c r="K16" t="n">
-        <v>379</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02241280635625142</v>
+        <v>0.02461485036482136</v>
       </c>
       <c r="M16" t="n">
-        <v>5.023169987303382</v>
+        <v>5.047161594126425</v>
       </c>
       <c r="N16" t="n">
-        <v>41.91430084039416</v>
+        <v>42.2033740545611</v>
       </c>
       <c r="O16" t="n">
-        <v>6.474125488465154</v>
+        <v>6.496412398744487</v>
       </c>
       <c r="P16" t="n">
-        <v>375.502019788686</v>
+        <v>375.5787621824821</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34312,28 +34397,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1135211307062384</v>
+        <v>-0.1206539901382703</v>
       </c>
       <c r="J17" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K17" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0151628979934777</v>
+        <v>0.01703459020806786</v>
       </c>
       <c r="M17" t="n">
-        <v>5.002378055377123</v>
+        <v>5.023318267629179</v>
       </c>
       <c r="N17" t="n">
-        <v>41.62104756167969</v>
+        <v>41.91985941615224</v>
       </c>
       <c r="O17" t="n">
-        <v>6.451437635262367</v>
+        <v>6.474554765862456</v>
       </c>
       <c r="P17" t="n">
-        <v>369.4515051643016</v>
+        <v>369.529025672985</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34390,28 +34475,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1214809473704147</v>
+        <v>-0.1249434989442286</v>
       </c>
       <c r="J18" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K18" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02616631010457626</v>
+        <v>0.02770946872416458</v>
       </c>
       <c r="M18" t="n">
-        <v>4.186296782815323</v>
+        <v>4.191222775026702</v>
       </c>
       <c r="N18" t="n">
-        <v>27.31090259671405</v>
+        <v>27.33537772962281</v>
       </c>
       <c r="O18" t="n">
-        <v>5.22598340953299</v>
+        <v>5.228324562383518</v>
       </c>
       <c r="P18" t="n">
-        <v>364.8179933737689</v>
+        <v>364.8556246718341</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34468,28 +34553,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1284656560632066</v>
+        <v>-0.1331365117410197</v>
       </c>
       <c r="J19" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K19" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02356002146471481</v>
+        <v>0.02528639145945588</v>
       </c>
       <c r="M19" t="n">
-        <v>4.532487559007614</v>
+        <v>4.543337627681653</v>
       </c>
       <c r="N19" t="n">
-        <v>34.01115270071629</v>
+        <v>34.09686224938672</v>
       </c>
       <c r="O19" t="n">
-        <v>5.831908152630346</v>
+        <v>5.839251856992188</v>
       </c>
       <c r="P19" t="n">
-        <v>366.5504108828924</v>
+        <v>366.6011741303084</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34546,28 +34631,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1386640969837769</v>
+        <v>-0.1432637130380541</v>
       </c>
       <c r="J20" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K20" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02396476134133874</v>
+        <v>0.02558563698858596</v>
       </c>
       <c r="M20" t="n">
-        <v>5.057030704730954</v>
+        <v>5.064545045545864</v>
       </c>
       <c r="N20" t="n">
-        <v>38.94017035158669</v>
+        <v>39.00764605096837</v>
       </c>
       <c r="O20" t="n">
-        <v>6.240205954260379</v>
+        <v>6.245610142409496</v>
       </c>
       <c r="P20" t="n">
-        <v>373.3436011178872</v>
+        <v>373.3935901271581</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34624,28 +34709,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1267717919855496</v>
+        <v>-0.1283902266847105</v>
       </c>
       <c r="J21" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K21" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02412657984436239</v>
+        <v>0.02486545723869793</v>
       </c>
       <c r="M21" t="n">
-        <v>4.543404010762731</v>
+        <v>4.538026791062796</v>
       </c>
       <c r="N21" t="n">
-        <v>32.32364951230331</v>
+        <v>32.25981831352051</v>
       </c>
       <c r="O21" t="n">
-        <v>5.685389125847352</v>
+        <v>5.679772734319615</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3164134460536</v>
+        <v>366.3340027287733</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34702,28 +34787,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1214082805402186</v>
+        <v>-0.1205940059636745</v>
       </c>
       <c r="J22" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K22" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02303898730346166</v>
+        <v>0.02287239477598091</v>
       </c>
       <c r="M22" t="n">
-        <v>4.455140304819031</v>
+        <v>4.447290601472471</v>
       </c>
       <c r="N22" t="n">
-        <v>31.08049067008447</v>
+        <v>31.00423237263813</v>
       </c>
       <c r="O22" t="n">
-        <v>5.574987952460926</v>
+        <v>5.568144428141042</v>
       </c>
       <c r="P22" t="n">
-        <v>366.0696888601908</v>
+        <v>366.0608392564683</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34761,7 +34846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W381"/>
+  <dimension ref="A1:W382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79337,6 +79422,123 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-37.61817041886046,177.94408747341058</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-37.618132056240846,177.94501351108835</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-37.61799569676122,177.9459005761042</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-37.61768606577795,177.94671872751647</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-37.61737420579768,177.9475359910786</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-37.61707497738238,177.94832636063458</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-37.61686842592075,177.94908153502203</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-37.61658313134792,177.9498539668778</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-37.61626977528108,177.9506749164845</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-37.61595240048134,177.9514922374106</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-37.61552250510471,177.95220788170045</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>-37.6152327574568,177.95304217829997</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>-37.61474147364179,177.95366740259254</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>-37.61426691691854,177.95433640005794</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>-37.61378212708364,177.95499879309256</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>-37.613273001618204,177.95563246908523</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>-37.61269484381017,177.95615829142733</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>-37.612128368254545,177.9567029816498</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>-37.61152308507155,177.95716657243827</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>-37.61087748456599,177.95753709927237</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>-37.610209851520445,177.95784702846092</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W382"/>
+  <dimension ref="A1:W384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29118,6 +29118,156 @@
       <c r="W382" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:53:55+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>394.24</v>
+      </c>
+      <c r="C383" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="D383" t="n">
+        <v>368.94</v>
+      </c>
+      <c r="E383" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="F383" t="n">
+        <v>397.32</v>
+      </c>
+      <c r="G383" t="n">
+        <v>411.24</v>
+      </c>
+      <c r="H383" t="n">
+        <v>409.37</v>
+      </c>
+      <c r="I383" t="n">
+        <v>398.98</v>
+      </c>
+      <c r="J383" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="K383" t="n">
+        <v>376.8</v>
+      </c>
+      <c r="L383" t="n">
+        <v>380.19</v>
+      </c>
+      <c r="M383" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="N383" t="n">
+        <v>372.47</v>
+      </c>
+      <c r="O383" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="P383" t="n">
+        <v>360.75</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>355.03</v>
+      </c>
+      <c r="R383" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="S383" t="n">
+        <v>356.54</v>
+      </c>
+      <c r="T383" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="U383" t="n">
+        <v>361.3</v>
+      </c>
+      <c r="V383" t="n">
+        <v>364.99</v>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="C384" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="D384" t="n">
+        <v>368</v>
+      </c>
+      <c r="E384" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="F384" t="n">
+        <v>398.06</v>
+      </c>
+      <c r="G384" t="n">
+        <v>412.16</v>
+      </c>
+      <c r="H384" t="n">
+        <v>412.77</v>
+      </c>
+      <c r="I384" t="n">
+        <v>399.79</v>
+      </c>
+      <c r="J384" t="n">
+        <v>388.91</v>
+      </c>
+      <c r="K384" t="n">
+        <v>378.22</v>
+      </c>
+      <c r="L384" t="n">
+        <v>380.93</v>
+      </c>
+      <c r="M384" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="N384" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="O384" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="P384" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="R384" t="n">
+        <v>355.58</v>
+      </c>
+      <c r="S384" t="n">
+        <v>355</v>
+      </c>
+      <c r="T384" t="n">
+        <v>364.28</v>
+      </c>
+      <c r="U384" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="V384" t="n">
+        <v>362.05</v>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29132,7 +29282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B392"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33055,6 +33205,26 @@
       </c>
       <c r="B392" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -33223,28 +33393,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2104353865138127</v>
+        <v>-0.21427810310717</v>
       </c>
       <c r="J2" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1020549604215699</v>
+        <v>0.1062398531154651</v>
       </c>
       <c r="M2" t="n">
-        <v>3.701541275113587</v>
+        <v>3.699099839700126</v>
       </c>
       <c r="N2" t="n">
-        <v>19.44388641936075</v>
+        <v>19.41454939128568</v>
       </c>
       <c r="O2" t="n">
-        <v>4.409522243890005</v>
+        <v>4.406194434121772</v>
       </c>
       <c r="P2" t="n">
-        <v>401.6227035058139</v>
+        <v>401.6646250759898</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33301,28 +33471,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002276722580527053</v>
+        <v>-0.004599209133824238</v>
       </c>
       <c r="J3" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L3" t="n">
-        <v>7.711975524404835e-06</v>
+        <v>3.167793577907307e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.640111403672428</v>
+        <v>4.648317736646399</v>
       </c>
       <c r="N3" t="n">
-        <v>33.54139587552681</v>
+        <v>33.56092246583886</v>
       </c>
       <c r="O3" t="n">
-        <v>5.791493406326801</v>
+        <v>5.79317896028069</v>
       </c>
       <c r="P3" t="n">
-        <v>381.1160645093432</v>
+        <v>381.1910564911858</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33379,28 +33549,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147867097424045</v>
+        <v>0.1412232718204476</v>
       </c>
       <c r="J4" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K4" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03087151054189852</v>
+        <v>0.02843314426013821</v>
       </c>
       <c r="M4" t="n">
-        <v>4.561600483255908</v>
+        <v>4.5682891391871</v>
       </c>
       <c r="N4" t="n">
-        <v>34.25283094171469</v>
+        <v>34.25299451663872</v>
       </c>
       <c r="O4" t="n">
-        <v>5.852591814035444</v>
+        <v>5.852605788590131</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4556627950626</v>
+        <v>370.5281191566548</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -33461,28 +33631,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2062838862455886</v>
+        <v>0.2013271495589387</v>
       </c>
       <c r="J5" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K5" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08778020964930333</v>
+        <v>0.08456947609366683</v>
       </c>
       <c r="M5" t="n">
-        <v>3.578693541644987</v>
+        <v>3.582996241969234</v>
       </c>
       <c r="N5" t="n">
-        <v>22.06802056048243</v>
+        <v>22.05233816720713</v>
       </c>
       <c r="O5" t="n">
-        <v>4.697661179830068</v>
+        <v>4.695991712855457</v>
       </c>
       <c r="P5" t="n">
-        <v>381.5846692597545</v>
+        <v>381.6387262440206</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33539,28 +33709,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1457265373869898</v>
+        <v>0.1391826449871522</v>
       </c>
       <c r="J6" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K6" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07326237201551433</v>
+        <v>0.06723026233838714</v>
       </c>
       <c r="M6" t="n">
-        <v>3.027310638994447</v>
+        <v>3.041029701256708</v>
       </c>
       <c r="N6" t="n">
-        <v>13.40549969699011</v>
+        <v>13.50883874636809</v>
       </c>
       <c r="O6" t="n">
-        <v>3.661352167845933</v>
+        <v>3.675437218395668</v>
       </c>
       <c r="P6" t="n">
-        <v>399.6445795897293</v>
+        <v>399.7159373442655</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33617,28 +33787,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05698637575815432</v>
+        <v>0.0498810809719842</v>
       </c>
       <c r="J7" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K7" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008977339017389285</v>
+        <v>0.006899273619798918</v>
       </c>
       <c r="M7" t="n">
-        <v>3.395831835692029</v>
+        <v>3.416110815723301</v>
       </c>
       <c r="N7" t="n">
-        <v>17.88990064374842</v>
+        <v>18.00113332368662</v>
       </c>
       <c r="O7" t="n">
-        <v>4.229645451305394</v>
+        <v>4.242774248494329</v>
       </c>
       <c r="P7" t="n">
-        <v>416.4964187322734</v>
+        <v>416.5738976175642</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33695,28 +33865,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02321356270513545</v>
+        <v>-0.0321604219727928</v>
       </c>
       <c r="J8" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K8" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001233185599942455</v>
+        <v>0.00235699313720239</v>
       </c>
       <c r="M8" t="n">
-        <v>3.677236733984355</v>
+        <v>3.701915294908233</v>
       </c>
       <c r="N8" t="n">
-        <v>21.77956249819383</v>
+        <v>22.0038424414422</v>
       </c>
       <c r="O8" t="n">
-        <v>4.666857882793714</v>
+        <v>4.690825347573942</v>
       </c>
       <c r="P8" t="n">
-        <v>419.6142727932772</v>
+        <v>419.711821000875</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33773,28 +33943,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.106450855227054</v>
+        <v>-0.1133140551072059</v>
       </c>
       <c r="J9" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K9" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02706471044789704</v>
+        <v>0.03064610986582328</v>
       </c>
       <c r="M9" t="n">
-        <v>3.579020523887274</v>
+        <v>3.589774811350591</v>
       </c>
       <c r="N9" t="n">
-        <v>20.3286610762177</v>
+        <v>20.41327901595601</v>
       </c>
       <c r="O9" t="n">
-        <v>4.508731648281776</v>
+        <v>4.518105688887325</v>
       </c>
       <c r="P9" t="n">
-        <v>408.2807982320047</v>
+        <v>408.3556376156922</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33851,28 +34021,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1070362151180871</v>
+        <v>-0.1138845662571692</v>
       </c>
       <c r="J10" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K10" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02762600848842922</v>
+        <v>0.03124344610021457</v>
       </c>
       <c r="M10" t="n">
-        <v>3.608642141555983</v>
+        <v>3.624452594609292</v>
       </c>
       <c r="N10" t="n">
-        <v>20.12364165202064</v>
+        <v>20.21266941344859</v>
       </c>
       <c r="O10" t="n">
-        <v>4.485938213130074</v>
+        <v>4.495850243663438</v>
       </c>
       <c r="P10" t="n">
-        <v>396.8381890589078</v>
+        <v>396.9128605410109</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33929,28 +34099,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1790198556338802</v>
+        <v>-0.1891706428195688</v>
       </c>
       <c r="J11" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K11" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0737507722057269</v>
+        <v>0.0810278833985032</v>
       </c>
       <c r="M11" t="n">
-        <v>3.585886436601935</v>
+        <v>3.615982366332164</v>
       </c>
       <c r="N11" t="n">
-        <v>20.08600593281893</v>
+        <v>20.39921822929308</v>
       </c>
       <c r="O11" t="n">
-        <v>4.48174139512968</v>
+        <v>4.516549371953448</v>
       </c>
       <c r="P11" t="n">
-        <v>391.2319273183363</v>
+        <v>391.3426148408249</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34007,28 +34177,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1671444184498415</v>
+        <v>-0.171057695038755</v>
       </c>
       <c r="J12" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K12" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06226297796348279</v>
+        <v>0.06559496959637012</v>
       </c>
       <c r="M12" t="n">
-        <v>3.712989113232994</v>
+        <v>3.709615390346215</v>
       </c>
       <c r="N12" t="n">
-        <v>20.99736633560376</v>
+        <v>20.95019497659078</v>
       </c>
       <c r="O12" t="n">
-        <v>4.58228832960168</v>
+        <v>4.577138295550046</v>
       </c>
       <c r="P12" t="n">
-        <v>388.4370639699792</v>
+        <v>388.4797345972308</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34085,28 +34255,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1996456610376267</v>
+        <v>-0.2162137845565647</v>
       </c>
       <c r="J13" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K13" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05139657297702749</v>
+        <v>0.05875679638937259</v>
       </c>
       <c r="M13" t="n">
-        <v>4.783954143461603</v>
+        <v>4.822095520594944</v>
       </c>
       <c r="N13" t="n">
-        <v>36.71133465303591</v>
+        <v>37.63992132454353</v>
       </c>
       <c r="O13" t="n">
-        <v>6.058987923163068</v>
+        <v>6.135138248201383</v>
       </c>
       <c r="P13" t="n">
-        <v>389.460510610892</v>
+        <v>389.6411702772843</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34163,28 +34333,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1727171745647075</v>
+        <v>-0.1838820155814733</v>
       </c>
       <c r="J14" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K14" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L14" t="n">
-        <v>0.034995827663719</v>
+        <v>0.03948810053061491</v>
       </c>
       <c r="M14" t="n">
-        <v>5.000418829621645</v>
+        <v>5.034403573939891</v>
       </c>
       <c r="N14" t="n">
-        <v>41.05006661022907</v>
+        <v>41.33835799290635</v>
       </c>
       <c r="O14" t="n">
-        <v>6.407032590070779</v>
+        <v>6.429491270147768</v>
       </c>
       <c r="P14" t="n">
-        <v>387.1067052989291</v>
+        <v>387.2284567218169</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34241,28 +34411,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2251557469823451</v>
+        <v>-0.2334650295051715</v>
       </c>
       <c r="J15" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K15" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05712576544913106</v>
+        <v>0.06148378362283979</v>
       </c>
       <c r="M15" t="n">
-        <v>5.032699068868033</v>
+        <v>5.052435130394171</v>
       </c>
       <c r="N15" t="n">
-        <v>41.75588602157811</v>
+        <v>41.81798235739678</v>
       </c>
       <c r="O15" t="n">
-        <v>6.461879449632135</v>
+        <v>6.466682484659099</v>
       </c>
       <c r="P15" t="n">
-        <v>380.2789025827734</v>
+        <v>380.3695097637093</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34319,28 +34489,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1460247039232168</v>
+        <v>-0.1585136973662153</v>
       </c>
       <c r="J16" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K16" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02461485036482136</v>
+        <v>0.02881235394543535</v>
       </c>
       <c r="M16" t="n">
-        <v>5.047161594126425</v>
+        <v>5.086356851306307</v>
       </c>
       <c r="N16" t="n">
-        <v>42.2033740545611</v>
+        <v>42.6088676527431</v>
       </c>
       <c r="O16" t="n">
-        <v>6.496412398744487</v>
+        <v>6.52754683267329</v>
       </c>
       <c r="P16" t="n">
-        <v>375.5787621824821</v>
+        <v>375.7147956956157</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34397,28 +34567,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1206539901382703</v>
+        <v>-0.1337761134469363</v>
       </c>
       <c r="J17" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K17" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01703459020806786</v>
+        <v>0.02077583576319031</v>
       </c>
       <c r="M17" t="n">
-        <v>5.023318267629179</v>
+        <v>5.060156998725179</v>
       </c>
       <c r="N17" t="n">
-        <v>41.91985941615224</v>
+        <v>42.39542295263904</v>
       </c>
       <c r="O17" t="n">
-        <v>6.474554765862456</v>
+        <v>6.511176771724067</v>
       </c>
       <c r="P17" t="n">
-        <v>369.529025672985</v>
+        <v>369.6721265778719</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34475,28 +34645,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1249434989442286</v>
+        <v>-0.1309952180816128</v>
       </c>
       <c r="J18" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K18" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02770946872416458</v>
+        <v>0.03057935981497306</v>
       </c>
       <c r="M18" t="n">
-        <v>4.191222775026702</v>
+        <v>4.196995241254638</v>
       </c>
       <c r="N18" t="n">
-        <v>27.33537772962281</v>
+        <v>27.34216894855074</v>
       </c>
       <c r="O18" t="n">
-        <v>5.228324562383518</v>
+        <v>5.228973986218591</v>
       </c>
       <c r="P18" t="n">
-        <v>364.8556246718341</v>
+        <v>364.9216255793265</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34553,28 +34723,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1331365117410197</v>
+        <v>-0.1413968131608031</v>
       </c>
       <c r="J19" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K19" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02528639145945588</v>
+        <v>0.02854658816014144</v>
       </c>
       <c r="M19" t="n">
-        <v>4.543337627681653</v>
+        <v>4.560503581680725</v>
       </c>
       <c r="N19" t="n">
-        <v>34.09686224938672</v>
+        <v>34.19678012591153</v>
       </c>
       <c r="O19" t="n">
-        <v>5.839251856992188</v>
+        <v>5.847801306979533</v>
       </c>
       <c r="P19" t="n">
-        <v>366.6011741303084</v>
+        <v>366.6912613477508</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34631,28 +34801,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1432637130380541</v>
+        <v>-0.1498108664876451</v>
       </c>
       <c r="J20" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K20" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02558563698858596</v>
+        <v>0.02812650069188305</v>
       </c>
       <c r="M20" t="n">
-        <v>5.064545045545864</v>
+        <v>5.067459462480342</v>
       </c>
       <c r="N20" t="n">
-        <v>39.00764605096837</v>
+        <v>38.97793916222371</v>
       </c>
       <c r="O20" t="n">
-        <v>6.245610142409496</v>
+        <v>6.243231467935793</v>
       </c>
       <c r="P20" t="n">
-        <v>373.3935901271581</v>
+        <v>373.4649823280465</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34709,28 +34879,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1283902266847105</v>
+        <v>-0.131721632813882</v>
       </c>
       <c r="J21" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K21" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02486545723869793</v>
+        <v>0.02641291382133693</v>
       </c>
       <c r="M21" t="n">
-        <v>4.538026791062796</v>
+        <v>4.527632925018558</v>
       </c>
       <c r="N21" t="n">
-        <v>32.25981831352051</v>
+        <v>32.1448132099073</v>
       </c>
       <c r="O21" t="n">
-        <v>5.679772734319615</v>
+        <v>5.669639601412713</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3340027287733</v>
+        <v>366.3703456126507</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34787,28 +34957,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1205940059636745</v>
+        <v>-0.1198745488942267</v>
       </c>
       <c r="J22" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K22" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02287239477598091</v>
+        <v>0.02287222397799693</v>
       </c>
       <c r="M22" t="n">
-        <v>4.447290601472471</v>
+        <v>4.431810460978249</v>
       </c>
       <c r="N22" t="n">
-        <v>31.00423237263813</v>
+        <v>30.85568130969212</v>
       </c>
       <c r="O22" t="n">
-        <v>5.568144428141042</v>
+        <v>5.554789042771302</v>
       </c>
       <c r="P22" t="n">
-        <v>366.0608392564683</v>
+        <v>366.0530089837242</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34846,7 +35016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W382"/>
+  <dimension ref="A1:W384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79539,6 +79709,240 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:53:55+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-37.618160130557456,177.9440833817264</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-37.61812588327757,177.94501105602905</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-37.61799543955513,177.9459004738083</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-37.617684436809995,177.94671807963513</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-37.61737051919476,177.94753452480404</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-37.61706933450463,177.94832370663525</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-37.61686115729022,177.9490763358092</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>-37.61657042636984,177.94984248624962</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>-37.61626342282321,177.95066917615264</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>-37.61594298136516,177.95148372585984</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>-37.61552352733037,177.95220880543457</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>-37.615223430149825,177.9530324107115</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>-37.61473095239523,177.95365361735065</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>-37.61425588398267,177.95432074830316</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>-37.61377472501987,177.9549877127604</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>-37.6132671478387,177.95562258651395</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>-37.61268831826537,177.95614650998812</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>-37.61212040488171,177.95668832746543</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>-37.611515943560505,177.95714932675392</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>-37.61087371467122,177.95752487342946</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>-37.61020764159067,177.95783986165</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-37.61818705161646,177.9440940883027</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-37.61814131568559,177.94501719367815</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-37.618003498679094,177.94590367907927</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-37.61768992386,177.9467202619724</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-37.61736417480828,177.9475320014481</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-37.61706158607533,177.9483200623384</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>-37.61683458379964,177.94905732794336</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>-37.616564511983,177.9498371418206</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>-37.616249257571056,177.95065637587612</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>-37.61593261303484,177.95147435655846</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>-37.61551812413743,177.95220392284023</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>-37.61520139006496,177.95300933027158</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>-37.6147287111827,177.95365068084993</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>-37.614248966032456,177.95431093423224</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>-37.613775418963414,177.95498875154146</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>-37.61327053121596,177.95562829845863</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>-37.612694638281226,177.95615792035835</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>-37.6121282160882,177.95670270163353</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>-37.611512040640505,177.95713990178822</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>-37.61088219693252,177.95755238157759</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>-37.61021719628366,177.95787084757058</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W384"/>
+  <dimension ref="A1:W386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29266,6 +29266,156 @@
         <v>362.05</v>
       </c>
       <c r="W384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:53:39+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>391.68</v>
+      </c>
+      <c r="C385" t="n">
+        <v>374.94</v>
+      </c>
+      <c r="D385" t="n">
+        <v>369.43</v>
+      </c>
+      <c r="E385" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="F385" t="n">
+        <v>399.19</v>
+      </c>
+      <c r="G385" t="n">
+        <v>413.92</v>
+      </c>
+      <c r="H385" t="n">
+        <v>416.15</v>
+      </c>
+      <c r="I385" t="n">
+        <v>402.45</v>
+      </c>
+      <c r="J385" t="n">
+        <v>389.48</v>
+      </c>
+      <c r="K385" t="n">
+        <v>380.63</v>
+      </c>
+      <c r="L385" t="n">
+        <v>383.26</v>
+      </c>
+      <c r="M385" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="N385" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="O385" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="P385" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>357.27</v>
+      </c>
+      <c r="R385" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="S385" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="T385" t="n">
+        <v>367</v>
+      </c>
+      <c r="U385" t="n">
+        <v>360.64</v>
+      </c>
+      <c r="V385" t="n">
+        <v>363.35</v>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:53:45+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="C386" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="D386" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="E386" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="F386" t="n">
+        <v>400.3</v>
+      </c>
+      <c r="G386" t="n">
+        <v>414.95</v>
+      </c>
+      <c r="H386" t="n">
+        <v>417.32</v>
+      </c>
+      <c r="I386" t="n">
+        <v>403.22</v>
+      </c>
+      <c r="J386" t="n">
+        <v>390.26</v>
+      </c>
+      <c r="K386" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="L386" t="n">
+        <v>383.99</v>
+      </c>
+      <c r="M386" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="N386" t="n">
+        <v>377.4</v>
+      </c>
+      <c r="O386" t="n">
+        <v>372.78</v>
+      </c>
+      <c r="P386" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="R386" t="n">
+        <v>358.49</v>
+      </c>
+      <c r="S386" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="T386" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="U386" t="n">
+        <v>361.57</v>
+      </c>
+      <c r="V386" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="W386" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29282,7 +29432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33225,6 +33375,26 @@
       </c>
       <c r="B394" t="n">
         <v>0.84</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -33393,28 +33563,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.21427810310717</v>
+        <v>-0.2187389930180682</v>
       </c>
       <c r="J2" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1062398531154651</v>
+        <v>0.111001942363006</v>
       </c>
       <c r="M2" t="n">
-        <v>3.699099839700126</v>
+        <v>3.699625042445014</v>
       </c>
       <c r="N2" t="n">
-        <v>19.41454939128568</v>
+        <v>19.39604029685881</v>
       </c>
       <c r="O2" t="n">
-        <v>4.406194434121772</v>
+        <v>4.404093584025981</v>
       </c>
       <c r="P2" t="n">
-        <v>401.6646250759898</v>
+        <v>401.7133733141742</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33471,28 +33641,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.004599209133824238</v>
+        <v>-0.01070844713867449</v>
       </c>
       <c r="J3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L3" t="n">
-        <v>3.167793577907307e-05</v>
+        <v>0.0001730121232258464</v>
       </c>
       <c r="M3" t="n">
-        <v>4.648317736646399</v>
+        <v>4.652716632765794</v>
       </c>
       <c r="N3" t="n">
-        <v>33.56092246583886</v>
+        <v>33.54221518505215</v>
       </c>
       <c r="O3" t="n">
-        <v>5.79317896028069</v>
+        <v>5.791564139768474</v>
       </c>
       <c r="P3" t="n">
-        <v>381.1910564911858</v>
+        <v>381.2578166377377</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33549,28 +33719,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1412232718204476</v>
+        <v>0.136594203099706</v>
       </c>
       <c r="J4" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02843314426013821</v>
+        <v>0.02689827984494586</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5682891391871</v>
+        <v>4.565652576244381</v>
       </c>
       <c r="N4" t="n">
-        <v>34.25299451663872</v>
+        <v>34.165572092599</v>
       </c>
       <c r="O4" t="n">
-        <v>5.852605788590131</v>
+        <v>5.845132341752324</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5281191566548</v>
+        <v>370.5787034061302</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -33631,28 +33801,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2013271495589387</v>
+        <v>0.1982827894571723</v>
       </c>
       <c r="J5" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08456947609366683</v>
+        <v>0.08303207957742043</v>
       </c>
       <c r="M5" t="n">
-        <v>3.582996241969234</v>
+        <v>3.578517822780634</v>
       </c>
       <c r="N5" t="n">
-        <v>22.05233816720713</v>
+        <v>21.97701447318608</v>
       </c>
       <c r="O5" t="n">
-        <v>4.695991712855457</v>
+        <v>4.68796485409032</v>
       </c>
       <c r="P5" t="n">
-        <v>381.6387262440206</v>
+        <v>381.6719934624413</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33709,28 +33879,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1391826449871522</v>
+        <v>0.1351135820863179</v>
       </c>
       <c r="J6" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K6" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06723026233838714</v>
+        <v>0.06402503103104618</v>
       </c>
       <c r="M6" t="n">
-        <v>3.041029701256708</v>
+        <v>3.043405994891064</v>
       </c>
       <c r="N6" t="n">
-        <v>13.50883874636809</v>
+        <v>13.50836789150638</v>
       </c>
       <c r="O6" t="n">
-        <v>3.675437218395668</v>
+        <v>3.675373163572153</v>
       </c>
       <c r="P6" t="n">
-        <v>399.7159373442655</v>
+        <v>399.7604023219168</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33787,28 +33957,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0498810809719842</v>
+        <v>0.04602898942444444</v>
       </c>
       <c r="J7" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K7" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006899273619798918</v>
+        <v>0.005932270528808403</v>
       </c>
       <c r="M7" t="n">
-        <v>3.416110815723301</v>
+        <v>3.419100584123736</v>
       </c>
       <c r="N7" t="n">
-        <v>18.00113332368662</v>
+        <v>17.97001065270265</v>
       </c>
       <c r="O7" t="n">
-        <v>4.242774248494329</v>
+        <v>4.239104935325693</v>
       </c>
       <c r="P7" t="n">
-        <v>416.5738976175642</v>
+        <v>416.6159917019956</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33865,28 +34035,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0321604219727928</v>
+        <v>-0.03452706354226781</v>
       </c>
       <c r="J8" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K8" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00235699313720239</v>
+        <v>0.002745913742794093</v>
       </c>
       <c r="M8" t="n">
-        <v>3.701915294908233</v>
+        <v>3.694242248965171</v>
       </c>
       <c r="N8" t="n">
-        <v>22.0038424414422</v>
+        <v>21.9143527940017</v>
       </c>
       <c r="O8" t="n">
-        <v>4.690825347573942</v>
+        <v>4.681276833728347</v>
       </c>
       <c r="P8" t="n">
-        <v>419.711821000875</v>
+        <v>419.7376812809928</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33943,28 +34113,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1133140551072059</v>
+        <v>-0.1161232339469372</v>
       </c>
       <c r="J9" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K9" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03064610986582328</v>
+        <v>0.03246637962673227</v>
       </c>
       <c r="M9" t="n">
-        <v>3.589774811350591</v>
+        <v>3.58324776989281</v>
       </c>
       <c r="N9" t="n">
-        <v>20.41327901595601</v>
+        <v>20.34046484777923</v>
       </c>
       <c r="O9" t="n">
-        <v>4.518105688887325</v>
+        <v>4.510040448574627</v>
       </c>
       <c r="P9" t="n">
-        <v>408.3556376156922</v>
+        <v>408.3863351114787</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34021,28 +34191,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1138845662571692</v>
+        <v>-0.1183743970132909</v>
       </c>
       <c r="J10" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K10" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03124344610021457</v>
+        <v>0.03393492896110673</v>
       </c>
       <c r="M10" t="n">
-        <v>3.624452594609292</v>
+        <v>3.628609156273048</v>
       </c>
       <c r="N10" t="n">
-        <v>20.21266941344859</v>
+        <v>20.19135303508955</v>
       </c>
       <c r="O10" t="n">
-        <v>4.495850243663438</v>
+        <v>4.493478945659983</v>
       </c>
       <c r="P10" t="n">
-        <v>396.9128605410109</v>
+        <v>396.9619246666296</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34099,28 +34269,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1891706428195688</v>
+        <v>-0.1949006872121635</v>
       </c>
       <c r="J11" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K11" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0810278833985032</v>
+        <v>0.08601761271637787</v>
       </c>
       <c r="M11" t="n">
-        <v>3.615982366332164</v>
+        <v>3.625000780392347</v>
       </c>
       <c r="N11" t="n">
-        <v>20.39921822929308</v>
+        <v>20.42996438241794</v>
       </c>
       <c r="O11" t="n">
-        <v>4.516549371953448</v>
+        <v>4.519951811957506</v>
       </c>
       <c r="P11" t="n">
-        <v>391.3426148408249</v>
+        <v>391.4052314280866</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34177,28 +34347,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.171057695038755</v>
+        <v>-0.1714271354500785</v>
       </c>
       <c r="J12" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K12" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06559496959637012</v>
+        <v>0.06661297368965591</v>
       </c>
       <c r="M12" t="n">
-        <v>3.709615390346215</v>
+        <v>3.692059825200713</v>
       </c>
       <c r="N12" t="n">
-        <v>20.95019497659078</v>
+        <v>20.8426291768365</v>
       </c>
       <c r="O12" t="n">
-        <v>4.577138295550046</v>
+        <v>4.565372840944812</v>
       </c>
       <c r="P12" t="n">
-        <v>388.4797345972308</v>
+        <v>388.4837700200241</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34255,28 +34425,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2162137845565647</v>
+        <v>-0.2239879497928352</v>
       </c>
       <c r="J13" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K13" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05875679638937259</v>
+        <v>0.0631084282065324</v>
       </c>
       <c r="M13" t="n">
-        <v>4.822095520594944</v>
+        <v>4.827693664805867</v>
       </c>
       <c r="N13" t="n">
-        <v>37.63992132454353</v>
+        <v>37.70003076605327</v>
       </c>
       <c r="O13" t="n">
-        <v>6.135138248201383</v>
+        <v>6.140035078568629</v>
       </c>
       <c r="P13" t="n">
-        <v>389.6411702772843</v>
+        <v>389.7261224868072</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34333,28 +34503,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1838820155814733</v>
+        <v>-0.1904823811654131</v>
       </c>
       <c r="J14" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K14" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03948810053061491</v>
+        <v>0.04256756834100306</v>
       </c>
       <c r="M14" t="n">
-        <v>5.034403573939891</v>
+        <v>5.043468765173229</v>
       </c>
       <c r="N14" t="n">
-        <v>41.33835799290635</v>
+        <v>41.30754098375786</v>
       </c>
       <c r="O14" t="n">
-        <v>6.429491270147768</v>
+        <v>6.42709428776005</v>
       </c>
       <c r="P14" t="n">
-        <v>387.2284567218169</v>
+        <v>387.3005824100382</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34411,28 +34581,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2334650295051715</v>
+        <v>-0.2360522952928123</v>
       </c>
       <c r="J15" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K15" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06148378362283979</v>
+        <v>0.0634462709399094</v>
       </c>
       <c r="M15" t="n">
-        <v>5.052435130394171</v>
+        <v>5.040382718694939</v>
       </c>
       <c r="N15" t="n">
-        <v>41.81798235739678</v>
+        <v>41.63259468204637</v>
       </c>
       <c r="O15" t="n">
-        <v>6.466682484659099</v>
+        <v>6.452332499340558</v>
       </c>
       <c r="P15" t="n">
-        <v>380.3695097637093</v>
+        <v>380.3977793822126</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34489,28 +34659,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1585136973662153</v>
+        <v>-0.1667501970642425</v>
       </c>
       <c r="J16" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K16" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02881235394543535</v>
+        <v>0.03196289991846246</v>
       </c>
       <c r="M16" t="n">
-        <v>5.086356851306307</v>
+        <v>5.103426654902384</v>
       </c>
       <c r="N16" t="n">
-        <v>42.6088676527431</v>
+        <v>42.66680449278701</v>
       </c>
       <c r="O16" t="n">
-        <v>6.52754683267329</v>
+        <v>6.531983197527915</v>
       </c>
       <c r="P16" t="n">
-        <v>375.7147956956157</v>
+        <v>375.804697255605</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34567,28 +34737,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1337761134469363</v>
+        <v>-0.142801238897158</v>
       </c>
       <c r="J17" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K17" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02077583576319031</v>
+        <v>0.02370352469277981</v>
       </c>
       <c r="M17" t="n">
-        <v>5.060156998725179</v>
+        <v>5.077406541048354</v>
       </c>
       <c r="N17" t="n">
-        <v>42.39542295263904</v>
+        <v>42.51313862844888</v>
       </c>
       <c r="O17" t="n">
-        <v>6.511176771724067</v>
+        <v>6.520210014136729</v>
       </c>
       <c r="P17" t="n">
-        <v>369.6721265778719</v>
+        <v>369.770751770666</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34645,28 +34815,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1309952180816128</v>
+        <v>-0.134746878367721</v>
       </c>
       <c r="J18" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K18" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03057935981497306</v>
+        <v>0.0326151605545455</v>
       </c>
       <c r="M18" t="n">
-        <v>4.196995241254638</v>
+        <v>4.192454620711839</v>
       </c>
       <c r="N18" t="n">
-        <v>27.34216894855074</v>
+        <v>27.25885496447326</v>
       </c>
       <c r="O18" t="n">
-        <v>5.228973986218591</v>
+        <v>5.221001337336858</v>
       </c>
       <c r="P18" t="n">
-        <v>364.9216255793265</v>
+        <v>364.9626226975994</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34723,28 +34893,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1413968131608031</v>
+        <v>-0.1474240481597143</v>
       </c>
       <c r="J19" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K19" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02854658816014144</v>
+        <v>0.03118691602990409</v>
       </c>
       <c r="M19" t="n">
-        <v>4.560503581680725</v>
+        <v>4.566462859927291</v>
       </c>
       <c r="N19" t="n">
-        <v>34.19678012591153</v>
+        <v>34.17390882102318</v>
       </c>
       <c r="O19" t="n">
-        <v>5.847801306979533</v>
+        <v>5.845845432529257</v>
       </c>
       <c r="P19" t="n">
-        <v>366.6912613477508</v>
+        <v>366.7571233909662</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34801,28 +34971,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1498108664876451</v>
+        <v>-0.1519619183688949</v>
       </c>
       <c r="J20" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K20" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02812650069188305</v>
+        <v>0.02924688182596624</v>
       </c>
       <c r="M20" t="n">
-        <v>5.067459462480342</v>
+        <v>5.050788025818274</v>
       </c>
       <c r="N20" t="n">
-        <v>38.97793916222371</v>
+        <v>38.79619967246124</v>
       </c>
       <c r="O20" t="n">
-        <v>6.243231467935793</v>
+        <v>6.22865954058024</v>
       </c>
       <c r="P20" t="n">
-        <v>373.4649823280465</v>
+        <v>373.4884866400777</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34879,28 +35049,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.131721632813882</v>
+        <v>-0.1337071841017821</v>
       </c>
       <c r="J21" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K21" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02641291382133693</v>
+        <v>0.02750445243514033</v>
       </c>
       <c r="M21" t="n">
-        <v>4.527632925018558</v>
+        <v>4.511998090255615</v>
       </c>
       <c r="N21" t="n">
-        <v>32.1448132099073</v>
+        <v>31.99517798936371</v>
       </c>
       <c r="O21" t="n">
-        <v>5.669639601412713</v>
+        <v>5.656428023882538</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3703456126507</v>
+        <v>366.3920418436239</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34957,28 +35127,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1198745488942267</v>
+        <v>-0.1189081539536325</v>
       </c>
       <c r="J22" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K22" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02287222397799693</v>
+        <v>0.02278067417208129</v>
       </c>
       <c r="M22" t="n">
-        <v>4.431810460978249</v>
+        <v>4.4133217944643</v>
       </c>
       <c r="N22" t="n">
-        <v>30.85568130969212</v>
+        <v>30.70005653322322</v>
       </c>
       <c r="O22" t="n">
-        <v>5.554789042771302</v>
+        <v>5.540763172454064</v>
       </c>
       <c r="P22" t="n">
-        <v>366.0530089837242</v>
+        <v>366.0424458478122</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35016,7 +35186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W384"/>
+  <dimension ref="A1:W386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79943,6 +80113,240 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:53:39+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-37.61818207893689,177.9440921106542</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-37.61813479978004,177.94501460222594</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-37.61799123852238,177.9458988029759</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-37.6176775779974,177.94671535171406</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-37.61735448675849,177.94752814821635</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-37.617046762992715,177.94831309064242</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>-37.61680816661962,177.94903843190272</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>-37.61654508942655,177.9498195909859</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>-37.616245095615184,177.95065261497106</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>-37.61591501607768,177.95145845514472</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>-37.6155011113796,177.95218854927106</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>-37.61516905538492,177.95297546933787</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>-37.61471215110967,177.95362898337774</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>-37.61422862963879,177.95428208425832</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>-37.61375847517254,177.9549633879764</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>-37.61325511805034,177.9556022773814</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>-37.61268379662725,177.9561383464724</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>-37.61212045560384,177.9566884208042</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>-37.61150074708012,177.95711262955226</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>-37.610875859611525,177.95753182951236</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>-37.61021297142049,177.95785714631228</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:53:45+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-37.61817667757799,177.9440899625191</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-37.618123739887515,177.945010203578</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-37.61797957851287,177.9458941655646</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-37.61766951889248,177.94671214640758</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-37.61734497017838,177.94752436318453</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-37.617038088120204,177.94830901061724</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>-37.61679902221023,177.94903189096888</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>-37.61653946710696,177.9498145104829</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>-37.61623940030691,177.95064746847015</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>-37.61590669220489,177.95145093331683</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>-37.61549578120173,177.95218373266073</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>-37.615152957131656,177.95295861123458</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>-37.614700260227245,177.95361340361984</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>-37.61421777560713,177.9542666863314</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>-37.613751593562824,177.95495308673648</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>-37.61324695497739,177.95558849618791</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>-37.61267968604658,177.9561309250953</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>-37.612110159010456,177.95666947304156</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>-37.6114960137476,177.9571011992792</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>-37.610872837195544,177.9575220277593</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>-37.61021037150385,177.95784871476943</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W386"/>
+  <dimension ref="A1:W389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29416,6 +29416,231 @@
         <v>364.15</v>
       </c>
       <c r="W386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>392.49</v>
+      </c>
+      <c r="C387" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="D387" t="n">
+        <v>372.01</v>
+      </c>
+      <c r="E387" t="n">
+        <v>385.36</v>
+      </c>
+      <c r="F387" t="n">
+        <v>401.27</v>
+      </c>
+      <c r="G387" t="n">
+        <v>415.72</v>
+      </c>
+      <c r="H387" t="n">
+        <v>418.45</v>
+      </c>
+      <c r="I387" t="n">
+        <v>404.21</v>
+      </c>
+      <c r="J387" t="n">
+        <v>391.17</v>
+      </c>
+      <c r="K387" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="L387" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="M387" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="N387" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="O387" t="n">
+        <v>373.07</v>
+      </c>
+      <c r="P387" t="n">
+        <v>365.14</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>359.28</v>
+      </c>
+      <c r="R387" t="n">
+        <v>358.88</v>
+      </c>
+      <c r="S387" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="T387" t="n">
+        <v>368.18</v>
+      </c>
+      <c r="U387" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="V387" t="n">
+        <v>363.83</v>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:16+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>393.03</v>
+      </c>
+      <c r="C388" t="n">
+        <v>377.76</v>
+      </c>
+      <c r="D388" t="n">
+        <v>372.85</v>
+      </c>
+      <c r="E388" t="n">
+        <v>385.73</v>
+      </c>
+      <c r="F388" t="n">
+        <v>402.05</v>
+      </c>
+      <c r="G388" t="n">
+        <v>416.89</v>
+      </c>
+      <c r="H388" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="I388" t="n">
+        <v>405.09</v>
+      </c>
+      <c r="J388" t="n">
+        <v>392.28</v>
+      </c>
+      <c r="K388" t="n">
+        <v>383.89</v>
+      </c>
+      <c r="L388" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="M388" t="n">
+        <v>380.59</v>
+      </c>
+      <c r="N388" t="n">
+        <v>379.31</v>
+      </c>
+      <c r="O388" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="P388" t="n">
+        <v>365.77</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="R388" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="S388" t="n">
+        <v>359.11</v>
+      </c>
+      <c r="T388" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="U388" t="n">
+        <v>362.14</v>
+      </c>
+      <c r="V388" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:24+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>394.85</v>
+      </c>
+      <c r="C389" t="n">
+        <v>380.69</v>
+      </c>
+      <c r="D389" t="n">
+        <v>374.59</v>
+      </c>
+      <c r="E389" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="F389" t="n">
+        <v>404.68</v>
+      </c>
+      <c r="G389" t="n">
+        <v>419.88</v>
+      </c>
+      <c r="H389" t="n">
+        <v>421.73</v>
+      </c>
+      <c r="I389" t="n">
+        <v>408.05</v>
+      </c>
+      <c r="J389" t="n">
+        <v>396.85</v>
+      </c>
+      <c r="K389" t="n">
+        <v>388.23</v>
+      </c>
+      <c r="L389" t="n">
+        <v>388.63</v>
+      </c>
+      <c r="M389" t="n">
+        <v>386.05</v>
+      </c>
+      <c r="N389" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="O389" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="P389" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="R389" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="S389" t="n">
+        <v>362.91</v>
+      </c>
+      <c r="T389" t="n">
+        <v>371.81</v>
+      </c>
+      <c r="U389" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="V389" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="W389" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29432,7 +29657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33395,6 +33620,36 @@
       </c>
       <c r="B396" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -33563,28 +33818,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2187389930180682</v>
+        <v>-0.2227583335065772</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K2" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L2" t="n">
-        <v>0.111001942363006</v>
+        <v>0.1162145937494595</v>
       </c>
       <c r="M2" t="n">
-        <v>3.699625042445014</v>
+        <v>3.688563433326048</v>
       </c>
       <c r="N2" t="n">
-        <v>19.39604029685881</v>
+        <v>19.29940448459569</v>
       </c>
       <c r="O2" t="n">
-        <v>4.404093584025981</v>
+        <v>4.393108749461557</v>
       </c>
       <c r="P2" t="n">
-        <v>401.7133733141742</v>
+        <v>401.7574095777792</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33641,28 +33896,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01070844713867449</v>
+        <v>-0.0149516233441361</v>
       </c>
       <c r="J3" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K3" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001730121232258464</v>
+        <v>0.0003426487659191624</v>
       </c>
       <c r="M3" t="n">
-        <v>4.652716632765794</v>
+        <v>4.636576921634438</v>
       </c>
       <c r="N3" t="n">
-        <v>33.54221518505215</v>
+        <v>33.35558165693296</v>
       </c>
       <c r="O3" t="n">
-        <v>5.791564139768474</v>
+        <v>5.775429131842323</v>
       </c>
       <c r="P3" t="n">
-        <v>381.2578166377377</v>
+        <v>381.3042854997948</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33719,28 +33974,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.136594203099706</v>
+        <v>0.1348699045200973</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K4" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02689827984494586</v>
+        <v>0.02669504584659121</v>
       </c>
       <c r="M4" t="n">
-        <v>4.565652576244381</v>
+        <v>4.540209359444388</v>
       </c>
       <c r="N4" t="n">
-        <v>34.165572092599</v>
+        <v>33.91862148658816</v>
       </c>
       <c r="O4" t="n">
-        <v>5.845132341752324</v>
+        <v>5.823969564359704</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5787034061302</v>
+        <v>370.5975745958577</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -33801,28 +34056,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1982827894571723</v>
+        <v>0.1970971896453121</v>
       </c>
       <c r="J5" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08303207957742043</v>
+        <v>0.08346179811302024</v>
       </c>
       <c r="M5" t="n">
-        <v>3.578517822780634</v>
+        <v>3.559444490317094</v>
       </c>
       <c r="N5" t="n">
-        <v>21.97701447318608</v>
+        <v>21.81792921840363</v>
       </c>
       <c r="O5" t="n">
-        <v>4.68796485409032</v>
+        <v>4.670966625700041</v>
       </c>
       <c r="P5" t="n">
-        <v>381.6719934624413</v>
+        <v>381.6849631765247</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33879,28 +34134,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1351135820863179</v>
+        <v>0.1340090737313462</v>
       </c>
       <c r="J6" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K6" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06402503103104618</v>
+        <v>0.06403863481055616</v>
       </c>
       <c r="M6" t="n">
-        <v>3.043405994891064</v>
+        <v>3.031751995968772</v>
       </c>
       <c r="N6" t="n">
-        <v>13.50836789150638</v>
+        <v>13.42375751209965</v>
       </c>
       <c r="O6" t="n">
-        <v>3.675373163572153</v>
+        <v>3.663844635365923</v>
       </c>
       <c r="P6" t="n">
-        <v>399.7604023219168</v>
+        <v>399.7724664210047</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33957,28 +34212,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04602898942444444</v>
+        <v>0.04548221543972641</v>
       </c>
       <c r="J7" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K7" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005932270528808403</v>
+        <v>0.005890254317688748</v>
       </c>
       <c r="M7" t="n">
-        <v>3.419100584123736</v>
+        <v>3.406172998046732</v>
       </c>
       <c r="N7" t="n">
-        <v>17.97001065270265</v>
+        <v>17.85555433319283</v>
       </c>
       <c r="O7" t="n">
-        <v>4.239104935325693</v>
+        <v>4.225583312773852</v>
       </c>
       <c r="P7" t="n">
-        <v>416.6159917019956</v>
+        <v>416.6219310380163</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34035,28 +34290,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03452706354226781</v>
+        <v>-0.03275882406315452</v>
       </c>
       <c r="J8" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K8" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002745913742794093</v>
+        <v>0.002514970635274838</v>
       </c>
       <c r="M8" t="n">
-        <v>3.694242248965171</v>
+        <v>3.675428032130832</v>
       </c>
       <c r="N8" t="n">
-        <v>21.9143527940017</v>
+        <v>21.76806899840825</v>
       </c>
       <c r="O8" t="n">
-        <v>4.681276833728347</v>
+        <v>4.66562632434363</v>
       </c>
       <c r="P8" t="n">
-        <v>419.7376812809928</v>
+        <v>419.7182504646457</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34113,28 +34368,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1161232339469372</v>
+        <v>-0.1153247264817838</v>
       </c>
       <c r="J9" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K9" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03246637962673227</v>
+        <v>0.03256695329875903</v>
       </c>
       <c r="M9" t="n">
-        <v>3.58324776989281</v>
+        <v>3.566315413664112</v>
       </c>
       <c r="N9" t="n">
-        <v>20.34046484777923</v>
+        <v>20.20591324615042</v>
       </c>
       <c r="O9" t="n">
-        <v>4.510040448574627</v>
+        <v>4.495098802712842</v>
       </c>
       <c r="P9" t="n">
-        <v>408.3863351114787</v>
+        <v>408.3775283347879</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34191,28 +34446,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1183743970132909</v>
+        <v>-0.1189989573582761</v>
       </c>
       <c r="J10" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K10" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03393492896110673</v>
+        <v>0.03480610549391894</v>
       </c>
       <c r="M10" t="n">
-        <v>3.628609156273048</v>
+        <v>3.619473346248978</v>
       </c>
       <c r="N10" t="n">
-        <v>20.19135303508955</v>
+        <v>20.08330929802067</v>
       </c>
       <c r="O10" t="n">
-        <v>4.493478945659983</v>
+        <v>4.48144053826676</v>
       </c>
       <c r="P10" t="n">
-        <v>396.9619246666296</v>
+        <v>396.9686953791589</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34269,28 +34524,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1949006872121635</v>
+        <v>-0.1970580510810404</v>
       </c>
       <c r="J11" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K11" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08601761271637787</v>
+        <v>0.08899333717269664</v>
       </c>
       <c r="M11" t="n">
-        <v>3.625000780392347</v>
+        <v>3.617882252442791</v>
       </c>
       <c r="N11" t="n">
-        <v>20.42996438241794</v>
+        <v>20.33022838971088</v>
       </c>
       <c r="O11" t="n">
-        <v>4.519951811957506</v>
+        <v>4.508905453622961</v>
       </c>
       <c r="P11" t="n">
-        <v>391.4052314280866</v>
+        <v>391.4288089407664</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34347,28 +34602,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1714271354500785</v>
+        <v>-0.1680455008005025</v>
       </c>
       <c r="J12" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K12" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06661297368965591</v>
+        <v>0.0651002102482876</v>
       </c>
       <c r="M12" t="n">
-        <v>3.692059825200713</v>
+        <v>3.680819081430712</v>
       </c>
       <c r="N12" t="n">
-        <v>20.8426291768365</v>
+        <v>20.7408370733696</v>
       </c>
       <c r="O12" t="n">
-        <v>4.565372840944812</v>
+        <v>4.554210916653905</v>
       </c>
       <c r="P12" t="n">
-        <v>388.4837700200241</v>
+        <v>388.4466355619494</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34425,28 +34680,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2239879497928352</v>
+        <v>-0.2269996733852782</v>
       </c>
       <c r="J13" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K13" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0631084282065324</v>
+        <v>0.06565750635688006</v>
       </c>
       <c r="M13" t="n">
-        <v>4.827693664805867</v>
+        <v>4.814318619727859</v>
       </c>
       <c r="N13" t="n">
-        <v>37.70003076605327</v>
+        <v>37.50265473128515</v>
       </c>
       <c r="O13" t="n">
-        <v>6.140035078568629</v>
+        <v>6.123941111023615</v>
       </c>
       <c r="P13" t="n">
-        <v>389.7261224868072</v>
+        <v>389.7590500040922</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34503,28 +34758,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1904823811654131</v>
+        <v>-0.1925453807296044</v>
       </c>
       <c r="J14" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K14" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04256756834100306</v>
+        <v>0.04410882716901021</v>
       </c>
       <c r="M14" t="n">
-        <v>5.043468765173229</v>
+        <v>5.033685011298427</v>
       </c>
       <c r="N14" t="n">
-        <v>41.30754098375786</v>
+        <v>41.09026854086808</v>
       </c>
       <c r="O14" t="n">
-        <v>6.42709428776005</v>
+        <v>6.410169150722006</v>
       </c>
       <c r="P14" t="n">
-        <v>387.3005824100382</v>
+        <v>387.3230950027665</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34581,28 +34836,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2360522952928123</v>
+        <v>-0.234480138119284</v>
       </c>
       <c r="J15" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K15" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0634462709399094</v>
+        <v>0.06365996689025566</v>
       </c>
       <c r="M15" t="n">
-        <v>5.040382718694939</v>
+        <v>5.014459284659496</v>
       </c>
       <c r="N15" t="n">
-        <v>41.63259468204637</v>
+        <v>41.35891494985298</v>
       </c>
       <c r="O15" t="n">
-        <v>6.452332499340558</v>
+        <v>6.431089717136046</v>
       </c>
       <c r="P15" t="n">
-        <v>380.3977793822126</v>
+        <v>380.3804705750035</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34659,28 +34914,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1667501970642425</v>
+        <v>-0.173336056319073</v>
       </c>
       <c r="J16" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K16" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03196289991846246</v>
+        <v>0.03491666550267203</v>
       </c>
       <c r="M16" t="n">
-        <v>5.103426654902384</v>
+        <v>5.098787555815393</v>
       </c>
       <c r="N16" t="n">
-        <v>42.66680449278701</v>
+        <v>42.51533747685004</v>
       </c>
       <c r="O16" t="n">
-        <v>6.531983197527915</v>
+        <v>6.520378629868824</v>
       </c>
       <c r="P16" t="n">
-        <v>375.804697255605</v>
+        <v>375.8767364026813</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34737,28 +34992,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.142801238897158</v>
+        <v>-0.1503238501597064</v>
       </c>
       <c r="J17" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K17" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02370352469277981</v>
+        <v>0.02653881703670824</v>
       </c>
       <c r="M17" t="n">
-        <v>5.077406541048354</v>
+        <v>5.074496544619172</v>
       </c>
       <c r="N17" t="n">
-        <v>42.51313862844888</v>
+        <v>42.39188123841817</v>
       </c>
       <c r="O17" t="n">
-        <v>6.520210014136729</v>
+        <v>6.510904794144833</v>
       </c>
       <c r="P17" t="n">
-        <v>369.770751770666</v>
+        <v>369.853153261939</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34815,28 +35070,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.134746878367721</v>
+        <v>-0.136214417296443</v>
       </c>
       <c r="J18" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K18" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0326151605545455</v>
+        <v>0.03384719920242973</v>
       </c>
       <c r="M18" t="n">
-        <v>4.192454620711839</v>
+        <v>4.17717288304186</v>
       </c>
       <c r="N18" t="n">
-        <v>27.25885496447326</v>
+        <v>27.08688500854646</v>
       </c>
       <c r="O18" t="n">
-        <v>5.221001337336858</v>
+        <v>5.204506221395691</v>
       </c>
       <c r="P18" t="n">
-        <v>364.9626226975994</v>
+        <v>364.9786508325805</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34893,28 +35148,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1474240481597143</v>
+        <v>-0.1519005544773311</v>
       </c>
       <c r="J19" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K19" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03118691602990409</v>
+        <v>0.03354620027494859</v>
       </c>
       <c r="M19" t="n">
-        <v>4.566462859927291</v>
+        <v>4.553803472841803</v>
       </c>
       <c r="N19" t="n">
-        <v>34.17390882102318</v>
+        <v>33.99744745317305</v>
       </c>
       <c r="O19" t="n">
-        <v>5.845845432529257</v>
+        <v>5.830733011652399</v>
       </c>
       <c r="P19" t="n">
-        <v>366.7571233909662</v>
+        <v>366.8061414069589</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34971,28 +35226,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1519619183688949</v>
+        <v>-0.1518162982738505</v>
       </c>
       <c r="J20" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K20" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02924688182596624</v>
+        <v>0.02969516126941385</v>
       </c>
       <c r="M20" t="n">
-        <v>5.050788025818274</v>
+        <v>5.023323733348523</v>
       </c>
       <c r="N20" t="n">
-        <v>38.79619967246124</v>
+        <v>38.51670568735989</v>
       </c>
       <c r="O20" t="n">
-        <v>6.22865954058024</v>
+        <v>6.206182859645685</v>
       </c>
       <c r="P20" t="n">
-        <v>373.4884866400777</v>
+        <v>373.4868401778892</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35049,28 +35304,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1337071841017821</v>
+        <v>-0.1340108305297972</v>
       </c>
       <c r="J21" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K21" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02750445243514033</v>
+        <v>0.02810908258189193</v>
       </c>
       <c r="M21" t="n">
-        <v>4.511998090255615</v>
+        <v>4.485123816411097</v>
       </c>
       <c r="N21" t="n">
-        <v>31.99517798936371</v>
+        <v>31.75707392673037</v>
       </c>
       <c r="O21" t="n">
-        <v>5.656428023882538</v>
+        <v>5.635341509325799</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3920418436239</v>
+        <v>366.3953373562953</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35127,28 +35382,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1189081539536325</v>
+        <v>-0.117192948020702</v>
       </c>
       <c r="J22" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K22" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02278067417208129</v>
+        <v>0.02253113407702612</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4133217944643</v>
+        <v>4.387150931809006</v>
       </c>
       <c r="N22" t="n">
-        <v>30.70005653322322</v>
+        <v>30.47282166950357</v>
       </c>
       <c r="O22" t="n">
-        <v>5.540763172454064</v>
+        <v>5.520219349763519</v>
       </c>
       <c r="P22" t="n">
-        <v>366.0424458478122</v>
+        <v>366.0236288681726</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35186,7 +35441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W386"/>
+  <dimension ref="A1:W389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80347,6 +80602,357 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-37.61817513433257,177.94408934876625</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-37.61811979604982,177.94500863506826</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-37.61796911879823,177.94589000553523</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-37.61766386037191,177.94670989587368</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-37.61733665388751,177.94752105554497</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-37.6170316030212,177.94830596050198</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>-37.616790190429725,177.94902557365828</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>-37.61653223840994,177.94980797840876</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>-37.61623275578023,177.95064146422007</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>-37.61590055882454,177.95144539091845</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>-37.61549278754008,177.95218102744158</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>-37.6151456334618,177.95295094188535</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>-37.6146971474304,177.95360932515</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>-37.61421604611835,177.954264232816</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>-37.61374933824513,177.95494971070028</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>-37.613244323460066,177.95558405356698</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>-37.612677682138326,177.95612730717423</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>-37.612111427064015,177.9566718065096</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>-37.61149584766572,177.95710079821703</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>-37.610872479705414,177.9575208684122</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>-37.61021141147059,177.9578520873865</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:16+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>-37.6181705045963,177.94408750750796</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>-37.61811062234024,177.94500498657888</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-37.61796191702734,177.94588714125348</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-37.61766068817097,177.9467086342109</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-37.617329966560725,177.9475183957942</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-37.61702174903935,177.94830132591244</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>-37.616781983907636,177.94901970359237</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>-37.61652581290109,177.9498021721217</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>-37.61622465091749,177.9506341403561</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>-37.61589121272053,177.95143694536083</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>-37.61548891768466,177.95217753045125</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>-37.615135822506886,177.95294066785385</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>-37.61468836934238,177.9535978238669</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>-37.61421133475207,177.95425754910218</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>-37.6137456950394,177.9549442571038</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>-37.613240510444825,177.95557761630042</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>-37.61267603790581,177.95612433862374</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>-37.61210736929244,177.95666433941216</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>-37.61149397924464,177.95709628626753</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>-37.61087098474659,177.95751602023356</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>-37.61021287392363,177.95785683012943</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:24+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>-37.61815490067,177.94408130178743</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>-37.61808550180744,177.9449949958608</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-37.617946999073,177.94588120810045</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-37.61764525584169,177.94670249639373</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-37.61730741826579,177.9475094276641</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>-37.61699656664005,177.94828948196746</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>-37.61676455481652,177.94900723669497</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>-37.616504199823204,177.94978264189106</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>-37.61619128224231,177.95060398716777</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>-37.6158595235809,177.95140830965832</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>-37.61546190170917,177.95215311751045</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>-37.61509809868408,177.95290116350495</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>-37.61464846326599,177.95354553792606</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>-37.61418479603496,177.95421990035007</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>-37.613714294063506,177.9548972523176</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>-37.61321414155378,177.9555330994466</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>-37.6126545601108,177.95608556194492</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>-37.612088094870195,177.95662887071018</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>-37.611480775730236,177.95706440183048</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>-37.61086445242402,177.95749483580295</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>-37.610208974048376,177.95784418281536</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W389"/>
+  <dimension ref="A1:W392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29641,6 +29641,231 @@
         <v>364.58</v>
       </c>
       <c r="W389" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>396.01</v>
+      </c>
+      <c r="C390" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="D390" t="n">
+        <v>375.48</v>
+      </c>
+      <c r="E390" t="n">
+        <v>388.11</v>
+      </c>
+      <c r="F390" t="n">
+        <v>405.37</v>
+      </c>
+      <c r="G390" t="n">
+        <v>419.98</v>
+      </c>
+      <c r="H390" t="n">
+        <v>421.91</v>
+      </c>
+      <c r="I390" t="n">
+        <v>408.06</v>
+      </c>
+      <c r="J390" t="n">
+        <v>397.33</v>
+      </c>
+      <c r="K390" t="n">
+        <v>388.85</v>
+      </c>
+      <c r="L390" t="n">
+        <v>388.74</v>
+      </c>
+      <c r="M390" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="N390" t="n">
+        <v>386.41</v>
+      </c>
+      <c r="O390" t="n">
+        <v>378.72</v>
+      </c>
+      <c r="P390" t="n">
+        <v>371.44</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="R390" t="n">
+        <v>363.12</v>
+      </c>
+      <c r="S390" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="T390" t="n">
+        <v>371.65</v>
+      </c>
+      <c r="U390" t="n">
+        <v>363.95</v>
+      </c>
+      <c r="V390" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:52:47+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="C391" t="n">
+        <v>384.86</v>
+      </c>
+      <c r="D391" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="E391" t="n">
+        <v>389.18</v>
+      </c>
+      <c r="F391" t="n">
+        <v>407.01</v>
+      </c>
+      <c r="G391" t="n">
+        <v>421</v>
+      </c>
+      <c r="H391" t="n">
+        <v>423.04</v>
+      </c>
+      <c r="I391" t="n">
+        <v>409.17</v>
+      </c>
+      <c r="J391" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="K391" t="n">
+        <v>390.59</v>
+      </c>
+      <c r="L391" t="n">
+        <v>390.12</v>
+      </c>
+      <c r="M391" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="N391" t="n">
+        <v>388.12</v>
+      </c>
+      <c r="O391" t="n">
+        <v>379.85</v>
+      </c>
+      <c r="P391" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>366.56</v>
+      </c>
+      <c r="R391" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="S391" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="T391" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="U391" t="n">
+        <v>364.26</v>
+      </c>
+      <c r="V391" t="n">
+        <v>363.81</v>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>398.18</v>
+      </c>
+      <c r="C392" t="n">
+        <v>384.94</v>
+      </c>
+      <c r="D392" t="n">
+        <v>377.08</v>
+      </c>
+      <c r="E392" t="n">
+        <v>390.43</v>
+      </c>
+      <c r="F392" t="n">
+        <v>407.41</v>
+      </c>
+      <c r="G392" t="n">
+        <v>421.29</v>
+      </c>
+      <c r="H392" t="n">
+        <v>424.12</v>
+      </c>
+      <c r="I392" t="n">
+        <v>410.17</v>
+      </c>
+      <c r="J392" t="n">
+        <v>399.53</v>
+      </c>
+      <c r="K392" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="L392" t="n">
+        <v>390.24</v>
+      </c>
+      <c r="M392" t="n">
+        <v>388.8</v>
+      </c>
+      <c r="N392" t="n">
+        <v>387.89</v>
+      </c>
+      <c r="O392" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="P392" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="R392" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="S392" t="n">
+        <v>363.58</v>
+      </c>
+      <c r="T392" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="U392" t="n">
+        <v>363.49</v>
+      </c>
+      <c r="V392" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="W392" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29657,7 +29882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B399"/>
+  <dimension ref="A1:B402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33650,6 +33875,36 @@
       </c>
       <c r="B399" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -33818,28 +34073,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2227583335065772</v>
+        <v>-0.220631709494983</v>
       </c>
       <c r="J2" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K2" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1162145937494595</v>
+        <v>0.1159813797479796</v>
       </c>
       <c r="M2" t="n">
-        <v>3.688563433326048</v>
+        <v>3.670823931755629</v>
       </c>
       <c r="N2" t="n">
-        <v>19.29940448459569</v>
+        <v>19.17033345529142</v>
       </c>
       <c r="O2" t="n">
-        <v>4.393108749461557</v>
+        <v>4.378393935599151</v>
       </c>
       <c r="P2" t="n">
-        <v>401.7574095777792</v>
+        <v>401.7339694675664</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33896,28 +34151,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0149516233441361</v>
+        <v>-0.009870216087664691</v>
       </c>
       <c r="J3" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K3" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003426487659191624</v>
+        <v>0.0001516601748826618</v>
       </c>
       <c r="M3" t="n">
-        <v>4.636576921634438</v>
+        <v>4.624761539109879</v>
       </c>
       <c r="N3" t="n">
-        <v>33.35558165693296</v>
+        <v>33.18459825506878</v>
       </c>
       <c r="O3" t="n">
-        <v>5.775429131842323</v>
+        <v>5.760607455387737</v>
       </c>
       <c r="P3" t="n">
-        <v>381.3042854997948</v>
+        <v>381.2482956009462</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33974,28 +34229,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1348699045200973</v>
+        <v>0.1385688988252882</v>
       </c>
       <c r="J4" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02669504584659121</v>
+        <v>0.02859600684360608</v>
       </c>
       <c r="M4" t="n">
-        <v>4.540209359444388</v>
+        <v>4.522985529845471</v>
       </c>
       <c r="N4" t="n">
-        <v>33.91862148658816</v>
+        <v>33.7013027334981</v>
       </c>
       <c r="O4" t="n">
-        <v>5.823969564359704</v>
+        <v>5.805282312988585</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5975745958577</v>
+        <v>370.5568197962826</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -34056,28 +34311,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1970971896453121</v>
+        <v>0.2008217414074805</v>
       </c>
       <c r="J5" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K5" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08346179811302024</v>
+        <v>0.08762292242206393</v>
       </c>
       <c r="M5" t="n">
-        <v>3.559444490317094</v>
+        <v>3.549520401487901</v>
       </c>
       <c r="N5" t="n">
-        <v>21.81792921840363</v>
+        <v>21.69695332059983</v>
       </c>
       <c r="O5" t="n">
-        <v>4.670966625700041</v>
+        <v>4.657998853649476</v>
       </c>
       <c r="P5" t="n">
-        <v>381.6849631765247</v>
+        <v>381.6439225237942</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34134,28 +34389,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1340090737313462</v>
+        <v>0.1392738697450676</v>
       </c>
       <c r="J6" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K6" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06403863481055616</v>
+        <v>0.06955908993535687</v>
       </c>
       <c r="M6" t="n">
-        <v>3.031751995968772</v>
+        <v>3.033996417842259</v>
       </c>
       <c r="N6" t="n">
-        <v>13.42375751209965</v>
+        <v>13.40586547017642</v>
       </c>
       <c r="O6" t="n">
-        <v>3.663844635365923</v>
+        <v>3.661402118065758</v>
       </c>
       <c r="P6" t="n">
-        <v>399.7724664210047</v>
+        <v>399.7144621144451</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34212,28 +34467,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04548221543972641</v>
+        <v>0.0502079260878651</v>
       </c>
       <c r="J7" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K7" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005890254317688748</v>
+        <v>0.007270221072491201</v>
       </c>
       <c r="M7" t="n">
-        <v>3.406172998046732</v>
+        <v>3.398777601407327</v>
       </c>
       <c r="N7" t="n">
-        <v>17.85555433319283</v>
+        <v>17.78478679122342</v>
       </c>
       <c r="O7" t="n">
-        <v>4.225583312773852</v>
+        <v>4.217201298399618</v>
       </c>
       <c r="P7" t="n">
-        <v>416.6219310380163</v>
+        <v>416.5698703518082</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34290,28 +34545,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03275882406315452</v>
+        <v>-0.02599997869753291</v>
       </c>
       <c r="J8" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K8" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002514970635274838</v>
+        <v>0.00160417981333083</v>
       </c>
       <c r="M8" t="n">
-        <v>3.675428032130832</v>
+        <v>3.676852873000075</v>
       </c>
       <c r="N8" t="n">
-        <v>21.76806899840825</v>
+        <v>21.73783845136089</v>
       </c>
       <c r="O8" t="n">
-        <v>4.66562632434363</v>
+        <v>4.662385489356375</v>
       </c>
       <c r="P8" t="n">
-        <v>419.7182504646457</v>
+        <v>419.6437899955741</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34368,28 +34623,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1153247264817838</v>
+        <v>-0.109125249853891</v>
       </c>
       <c r="J9" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K9" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03256695329875903</v>
+        <v>0.02960672115259921</v>
       </c>
       <c r="M9" t="n">
-        <v>3.566315413664112</v>
+        <v>3.570192418524915</v>
       </c>
       <c r="N9" t="n">
-        <v>20.20591324615042</v>
+        <v>20.16641192952803</v>
       </c>
       <c r="O9" t="n">
-        <v>4.495098802712842</v>
+        <v>4.490702832467099</v>
       </c>
       <c r="P9" t="n">
-        <v>408.3775283347879</v>
+        <v>408.3092295917808</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34446,28 +34701,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1189989573582761</v>
+        <v>-0.111462404386438</v>
       </c>
       <c r="J10" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K10" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03480610549391894</v>
+        <v>0.03095101183251714</v>
       </c>
       <c r="M10" t="n">
-        <v>3.619473346248978</v>
+        <v>3.623657332768472</v>
       </c>
       <c r="N10" t="n">
-        <v>20.08330929802067</v>
+        <v>20.09779262644705</v>
       </c>
       <c r="O10" t="n">
-        <v>4.48144053826676</v>
+        <v>4.483056170342621</v>
       </c>
       <c r="P10" t="n">
-        <v>396.9686953791589</v>
+        <v>396.8856689942805</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34524,28 +34779,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1970580510810404</v>
+        <v>-0.1905797905483429</v>
       </c>
       <c r="J11" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K11" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08899333717269664</v>
+        <v>0.08461600910805167</v>
       </c>
       <c r="M11" t="n">
-        <v>3.617882252442791</v>
+        <v>3.619087250237564</v>
       </c>
       <c r="N11" t="n">
-        <v>20.33022838971088</v>
+        <v>20.30135991695704</v>
       </c>
       <c r="O11" t="n">
-        <v>4.508905453622961</v>
+        <v>4.505703043583436</v>
       </c>
       <c r="P11" t="n">
-        <v>391.4288089407664</v>
+        <v>391.3574374719107</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34602,28 +34857,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1680455008005025</v>
+        <v>-0.1587740183435577</v>
       </c>
       <c r="J12" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K12" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0651002102482876</v>
+        <v>0.05884763552202066</v>
       </c>
       <c r="M12" t="n">
-        <v>3.680819081430712</v>
+        <v>3.700198158170662</v>
       </c>
       <c r="N12" t="n">
-        <v>20.7408370733696</v>
+        <v>20.83101626154547</v>
       </c>
       <c r="O12" t="n">
-        <v>4.554210916653905</v>
+        <v>4.564100816321378</v>
       </c>
       <c r="P12" t="n">
-        <v>388.4466355619494</v>
+        <v>388.3445047761469</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34680,28 +34935,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2269996733852782</v>
+        <v>-0.2198745037854309</v>
       </c>
       <c r="J13" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K13" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06565750635688006</v>
+        <v>0.06265972094452388</v>
       </c>
       <c r="M13" t="n">
-        <v>4.814318619727859</v>
+        <v>4.815197851137508</v>
       </c>
       <c r="N13" t="n">
-        <v>37.50265473128515</v>
+        <v>37.36622576609334</v>
       </c>
       <c r="O13" t="n">
-        <v>6.123941111023615</v>
+        <v>6.112791977983002</v>
       </c>
       <c r="P13" t="n">
-        <v>389.7590500040922</v>
+        <v>389.6805552039689</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34758,28 +35013,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1925453807296044</v>
+        <v>-0.1840050135036058</v>
       </c>
       <c r="J14" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K14" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04410882716901021</v>
+        <v>0.04093295496294591</v>
       </c>
       <c r="M14" t="n">
-        <v>5.033685011298427</v>
+        <v>5.029136091391009</v>
       </c>
       <c r="N14" t="n">
-        <v>41.09026854086808</v>
+        <v>40.98791703218187</v>
       </c>
       <c r="O14" t="n">
-        <v>6.410169150722006</v>
+        <v>6.402180646637665</v>
       </c>
       <c r="P14" t="n">
-        <v>387.3230950027665</v>
+        <v>387.2290164532989</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34836,28 +35091,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.234480138119284</v>
+        <v>-0.226064621282522</v>
       </c>
       <c r="J15" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K15" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06365996689025566</v>
+        <v>0.06016685002197675</v>
       </c>
       <c r="M15" t="n">
-        <v>5.014459284659496</v>
+        <v>5.00844792743219</v>
       </c>
       <c r="N15" t="n">
-        <v>41.35891494985298</v>
+        <v>41.24576400526969</v>
       </c>
       <c r="O15" t="n">
-        <v>6.431089717136046</v>
+        <v>6.422286509123499</v>
       </c>
       <c r="P15" t="n">
-        <v>380.3804705750035</v>
+        <v>380.2877733820239</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34914,28 +35169,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.173336056319073</v>
+        <v>-0.1710386177497202</v>
       </c>
       <c r="J16" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K16" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03491666550267203</v>
+        <v>0.03460771095858861</v>
       </c>
       <c r="M16" t="n">
-        <v>5.098787555815393</v>
+        <v>5.068753006396443</v>
       </c>
       <c r="N16" t="n">
-        <v>42.51533747685004</v>
+        <v>42.20940983646947</v>
       </c>
       <c r="O16" t="n">
-        <v>6.520378629868824</v>
+        <v>6.496876929453833</v>
       </c>
       <c r="P16" t="n">
-        <v>375.8767364026813</v>
+        <v>375.8514448694798</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34992,28 +35247,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1503238501597064</v>
+        <v>-0.149819006047163</v>
       </c>
       <c r="J17" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K17" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02653881703670824</v>
+        <v>0.02682560802613043</v>
       </c>
       <c r="M17" t="n">
-        <v>5.074496544619172</v>
+        <v>5.041968763808135</v>
       </c>
       <c r="N17" t="n">
-        <v>42.39188123841817</v>
+        <v>42.07223526751368</v>
       </c>
       <c r="O17" t="n">
-        <v>6.510904794144833</v>
+        <v>6.486311376083767</v>
       </c>
       <c r="P17" t="n">
-        <v>369.853153261939</v>
+        <v>369.8475776686064</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35070,28 +35325,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.136214417296443</v>
+        <v>-0.1330889318724332</v>
       </c>
       <c r="J18" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K18" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03384719920242973</v>
+        <v>0.03289349079761983</v>
       </c>
       <c r="M18" t="n">
-        <v>4.17717288304186</v>
+        <v>4.159855472597812</v>
       </c>
       <c r="N18" t="n">
-        <v>27.08688500854646</v>
+        <v>26.90722347974514</v>
       </c>
       <c r="O18" t="n">
-        <v>5.204506221395691</v>
+        <v>5.187217315646718</v>
       </c>
       <c r="P18" t="n">
-        <v>364.9786508325805</v>
+        <v>364.9442248263753</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35148,28 +35403,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1519005544773311</v>
+        <v>-0.1503334374927842</v>
       </c>
       <c r="J19" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K19" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03354620027494859</v>
+        <v>0.03344662938181819</v>
       </c>
       <c r="M19" t="n">
-        <v>4.553803472841803</v>
+        <v>4.525627925715952</v>
       </c>
       <c r="N19" t="n">
-        <v>33.99744745317305</v>
+        <v>33.74468072058283</v>
       </c>
       <c r="O19" t="n">
-        <v>5.830733011652399</v>
+        <v>5.809017190591092</v>
       </c>
       <c r="P19" t="n">
-        <v>366.8061414069589</v>
+        <v>366.7888777784702</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35226,28 +35481,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1518162982738505</v>
+        <v>-0.1479187994706192</v>
       </c>
       <c r="J20" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K20" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02969516126941385</v>
+        <v>0.02869603561537359</v>
       </c>
       <c r="M20" t="n">
-        <v>5.023323733348523</v>
+        <v>5.003631889212422</v>
       </c>
       <c r="N20" t="n">
-        <v>38.51670568735989</v>
+        <v>38.26490776207776</v>
       </c>
       <c r="O20" t="n">
-        <v>6.206182859645685</v>
+        <v>6.185863542148159</v>
       </c>
       <c r="P20" t="n">
-        <v>373.4868401778892</v>
+        <v>373.4439104360303</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35304,28 +35559,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1340108305297972</v>
+        <v>-0.1322683846759102</v>
       </c>
       <c r="J21" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K21" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02810908258189193</v>
+        <v>0.02787588833896426</v>
       </c>
       <c r="M21" t="n">
-        <v>4.485123816411097</v>
+        <v>4.460024997445378</v>
       </c>
       <c r="N21" t="n">
-        <v>31.75707392673037</v>
+        <v>31.52287093441268</v>
       </c>
       <c r="O21" t="n">
-        <v>5.635341509325799</v>
+        <v>5.614523215234993</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3953373562953</v>
+        <v>366.3761482855063</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35382,28 +35637,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.117192948020702</v>
+        <v>-0.1148951154588624</v>
       </c>
       <c r="J22" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K22" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02253113407702612</v>
+        <v>0.02204667309547792</v>
       </c>
       <c r="M22" t="n">
-        <v>4.387150931809006</v>
+        <v>4.364116732832438</v>
       </c>
       <c r="N22" t="n">
-        <v>30.47282166950357</v>
+        <v>30.25511884193119</v>
       </c>
       <c r="O22" t="n">
-        <v>5.520219349763519</v>
+        <v>5.50046532958178</v>
       </c>
       <c r="P22" t="n">
-        <v>366.0236288681726</v>
+        <v>365.9983209913091</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35441,7 +35696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W389"/>
+  <dimension ref="A1:W392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80953,6 +81208,357 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>-37.6181449553101,177.94407734649457</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>-37.618071355431695,177.94498936969185</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-37.61793936862489,177.94587817332783</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-37.617640283202135,177.94670051865327</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-37.61730150255326,177.9475070748097</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-37.6169957244193,177.94828908584904</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-37.61676314798398,177.94900623039857</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>-37.616504126806035,177.9497825759106</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>-37.616187777435606,177.95060082009488</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>-37.61585499656024,177.9514042188457</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>-37.615461098531426,177.95215239172057</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>-37.61509257138266,177.95289537532537</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>-37.614644167602464,177.95353990964557</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>-37.61418235089405,177.95421643158997</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>-37.61371290617455,177.9548951747589</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>-37.61321333598654,177.95553173946172</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>-37.61265589605061,177.95608797389082</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>-37.61208581237202,177.95662467047032</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>-37.61148144005823,177.95706600607866</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>-37.61086510240655,177.95749694370633</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>-37.61020903904631,177.95784439360392</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:52:47+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-37.61813475274241,177.9440732889109</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-37.61804975005698,177.94498077700212</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-37.61792736567256,177.9458733995296</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-37.617631109539396,177.94669687006385</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-37.61728744201879,177.94750148251975</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-37.616987133767594,177.94828504544185</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-37.61675431620166,177.94899991309444</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>-37.616496021900765,177.94977525207713</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-37.616179161451974,177.9505930343754</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-37.615842291694825,177.95139273818086</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-37.615451022301,177.95214328635834</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>-37.615079858588096,177.9528820625157</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>-37.61463352182628,177.95352596130112</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>-37.61417561184646,177.95420687134992</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>-37.61370342226567,177.95488097810974</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>-37.613205226608684,177.95551804894902</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>-37.612653840758554,177.95608426320484</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>-37.612081348819565,177.95661645666868</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>-37.61147953011517,177.9570613938653</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>-37.61086409493361,177.95749367645607</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>-37.61021147646851,177.95785229817508</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-37.61812635062765,177.94406994737233</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-37.618049064172055,177.94498050421842</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-37.617925650965056,177.94587271755853</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-37.61762039264342,177.94669260769433</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-37.61728401262007,177.94750011854694</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-37.61698469132736,177.94828389669883</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-37.616745875205716,177.94899387531848</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-37.61648872018381,177.94976865403038</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-37.61617171373678,177.95058630434818</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-37.615838567854695,177.95138937315915</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>-37.61545014610702,177.95214249458786</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-37.61507909858402,177.95288126664136</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>-37.61463495371442,177.95352783739403</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>-37.61417811662532,177.9542104247133</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>-37.613701051288146,177.954877428948</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>-37.613203561769296,177.9555152383143</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>-37.61265548499222,177.9560872317536</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>-37.612084696483976,177.95662261701983</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>-37.611480817250744,177.957064502096</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>-37.61086659736622,177.95750179188425</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>-37.610208909050435,177.95784397202678</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0210/nzd0210.xlsx
+++ b/data/nzd0210/nzd0210.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W392"/>
+  <dimension ref="A1:W394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29866,6 +29866,156 @@
         <v>364.6</v>
       </c>
       <c r="W392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>400.33</v>
+      </c>
+      <c r="C393" t="n">
+        <v>386.28</v>
+      </c>
+      <c r="D393" t="n">
+        <v>378.58</v>
+      </c>
+      <c r="E393" t="n">
+        <v>392.27</v>
+      </c>
+      <c r="F393" t="n">
+        <v>407.76</v>
+      </c>
+      <c r="G393" t="n">
+        <v>422.07</v>
+      </c>
+      <c r="H393" t="n">
+        <v>426.32</v>
+      </c>
+      <c r="I393" t="n">
+        <v>412.9</v>
+      </c>
+      <c r="J393" t="n">
+        <v>401.46</v>
+      </c>
+      <c r="K393" t="n">
+        <v>392.62</v>
+      </c>
+      <c r="L393" t="n">
+        <v>391.78</v>
+      </c>
+      <c r="M393" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="N393" t="n">
+        <v>389.04</v>
+      </c>
+      <c r="O393" t="n">
+        <v>381.17</v>
+      </c>
+      <c r="P393" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>367.94</v>
+      </c>
+      <c r="R393" t="n">
+        <v>364.49</v>
+      </c>
+      <c r="S393" t="n">
+        <v>365.37</v>
+      </c>
+      <c r="T393" t="n">
+        <v>373.51</v>
+      </c>
+      <c r="U393" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="V393" t="n">
+        <v>364.71</v>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:53:09+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>401.95</v>
+      </c>
+      <c r="C394" t="n">
+        <v>387.59</v>
+      </c>
+      <c r="D394" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="E394" t="n">
+        <v>393.95</v>
+      </c>
+      <c r="F394" t="n">
+        <v>408.57</v>
+      </c>
+      <c r="G394" t="n">
+        <v>423.21</v>
+      </c>
+      <c r="H394" t="n">
+        <v>427.76</v>
+      </c>
+      <c r="I394" t="n">
+        <v>414.08</v>
+      </c>
+      <c r="J394" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="K394" t="n">
+        <v>392.63</v>
+      </c>
+      <c r="L394" t="n">
+        <v>390.06</v>
+      </c>
+      <c r="M394" t="n">
+        <v>389.42</v>
+      </c>
+      <c r="N394" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="O394" t="n">
+        <v>381.22</v>
+      </c>
+      <c r="P394" t="n">
+        <v>376.26</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="R394" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="S394" t="n">
+        <v>365.61</v>
+      </c>
+      <c r="T394" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="U394" t="n">
+        <v>363.16</v>
+      </c>
+      <c r="V394" t="n">
+        <v>363.55</v>
+      </c>
+      <c r="W394" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29882,7 +30032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B402"/>
+  <dimension ref="A1:B404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33905,6 +34055,26 @@
       </c>
       <c r="B402" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -34073,28 +34243,28 @@
         <v>0.0352</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.220631709494983</v>
+        <v>-0.2149587483813055</v>
       </c>
       <c r="J2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1159813797479796</v>
+        <v>0.1111683921615607</v>
       </c>
       <c r="M2" t="n">
-        <v>3.670823931755629</v>
+        <v>3.679975313034944</v>
       </c>
       <c r="N2" t="n">
-        <v>19.17033345529142</v>
+        <v>19.21693268931046</v>
       </c>
       <c r="O2" t="n">
-        <v>4.378393935599151</v>
+        <v>4.383712204206666</v>
       </c>
       <c r="P2" t="n">
-        <v>401.7339694675664</v>
+        <v>401.6712454021783</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34151,28 +34321,28 @@
         <v>0.0504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009870216087664691</v>
+        <v>-0.003506344280547633</v>
       </c>
       <c r="J3" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K3" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001516601748826618</v>
+        <v>1.926472404312207e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>4.624761539109879</v>
+        <v>4.630900934949568</v>
       </c>
       <c r="N3" t="n">
-        <v>33.18459825506878</v>
+        <v>33.19507142284504</v>
       </c>
       <c r="O3" t="n">
-        <v>5.760607455387737</v>
+        <v>5.761516416955265</v>
       </c>
       <c r="P3" t="n">
-        <v>381.2482956009462</v>
+        <v>381.1779350357653</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34229,28 +34399,28 @@
         <v>0.0418</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1385688988252882</v>
+        <v>0.1440577934734603</v>
       </c>
       <c r="J4" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K4" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02859600684360608</v>
+        <v>0.03106878815449343</v>
       </c>
       <c r="M4" t="n">
-        <v>4.522985529845471</v>
+        <v>4.525748806487287</v>
       </c>
       <c r="N4" t="n">
-        <v>33.7013027334981</v>
+        <v>33.66493674059548</v>
       </c>
       <c r="O4" t="n">
-        <v>5.805282312988585</v>
+        <v>5.802149320777214</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5568197962826</v>
+        <v>370.4961306565286</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -34311,28 +34481,28 @@
         <v>0.0581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2008217414074805</v>
+        <v>0.2073399650806748</v>
       </c>
       <c r="J5" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K5" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08762292242206393</v>
+        <v>0.09312618829078279</v>
       </c>
       <c r="M5" t="n">
-        <v>3.549520401487901</v>
+        <v>3.56186729793125</v>
       </c>
       <c r="N5" t="n">
-        <v>21.69695332059983</v>
+        <v>21.77593087457118</v>
       </c>
       <c r="O5" t="n">
-        <v>4.657998853649476</v>
+        <v>4.666468779984624</v>
       </c>
       <c r="P5" t="n">
-        <v>381.6439225237942</v>
+        <v>381.5718537272912</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34389,28 +34559,28 @@
         <v>0.0635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1392738697450676</v>
+        <v>0.1443280884010734</v>
       </c>
       <c r="J6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06955908993535687</v>
+        <v>0.07455196267425945</v>
       </c>
       <c r="M6" t="n">
-        <v>3.033996417842259</v>
+        <v>3.042754563031964</v>
       </c>
       <c r="N6" t="n">
-        <v>13.40586547017642</v>
+        <v>13.4502491821868</v>
       </c>
       <c r="O6" t="n">
-        <v>3.661402118065758</v>
+        <v>3.667458136391852</v>
       </c>
       <c r="P6" t="n">
-        <v>399.7144621144451</v>
+        <v>399.6585825573529</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34467,28 +34637,28 @@
         <v>0.0512</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0502079260878651</v>
+        <v>0.05526533980060136</v>
       </c>
       <c r="J7" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K7" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007270221072491201</v>
+        <v>0.008842468803938575</v>
       </c>
       <c r="M7" t="n">
-        <v>3.398777601407327</v>
+        <v>3.401583670879599</v>
       </c>
       <c r="N7" t="n">
-        <v>17.78478679122342</v>
+        <v>17.80780912670536</v>
       </c>
       <c r="O7" t="n">
-        <v>4.217201298399618</v>
+        <v>4.219929990735078</v>
       </c>
       <c r="P7" t="n">
-        <v>416.5698703518082</v>
+        <v>416.5139538287391</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34545,28 +34715,28 @@
         <v>0.0457</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02599997869753291</v>
+        <v>-0.01734652878393778</v>
       </c>
       <c r="J8" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K8" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00160417981333083</v>
+        <v>0.0007123095788316158</v>
       </c>
       <c r="M8" t="n">
-        <v>3.676852873000075</v>
+        <v>3.696100018535287</v>
       </c>
       <c r="N8" t="n">
-        <v>21.73783845136089</v>
+        <v>21.95748370131248</v>
       </c>
       <c r="O8" t="n">
-        <v>4.662385489356375</v>
+        <v>4.685881315325057</v>
       </c>
       <c r="P8" t="n">
-        <v>419.6437899955741</v>
+        <v>419.5481169972911</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34623,28 +34793,28 @@
         <v>0.055</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.109125249853891</v>
+        <v>-0.1004643601887463</v>
       </c>
       <c r="J9" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K9" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02960672115259921</v>
+        <v>0.02509710752785488</v>
       </c>
       <c r="M9" t="n">
-        <v>3.570192418524915</v>
+        <v>3.595807417450156</v>
       </c>
       <c r="N9" t="n">
-        <v>20.16641192952803</v>
+        <v>20.39376388628435</v>
       </c>
       <c r="O9" t="n">
-        <v>4.490702832467099</v>
+        <v>4.515945514096063</v>
       </c>
       <c r="P9" t="n">
-        <v>408.3092295917808</v>
+        <v>408.2134756881915</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34701,28 +34871,28 @@
         <v>0.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.111462404386438</v>
+        <v>-0.1032450739708065</v>
       </c>
       <c r="J10" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K10" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03095101183251714</v>
+        <v>0.02659867418542583</v>
       </c>
       <c r="M10" t="n">
-        <v>3.623657332768472</v>
+        <v>3.640575217043379</v>
       </c>
       <c r="N10" t="n">
-        <v>20.09779262644705</v>
+        <v>20.29113204499714</v>
       </c>
       <c r="O10" t="n">
-        <v>4.483056170342621</v>
+        <v>4.504567908800703</v>
       </c>
       <c r="P10" t="n">
-        <v>396.8856689942805</v>
+        <v>396.7948233810313</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34779,28 +34949,28 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1905797905483429</v>
+        <v>-0.1837771980629882</v>
       </c>
       <c r="J11" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K11" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08461600910805167</v>
+        <v>0.07928674861081519</v>
       </c>
       <c r="M11" t="n">
-        <v>3.619087250237564</v>
+        <v>3.631003174870469</v>
       </c>
       <c r="N11" t="n">
-        <v>20.30135991695704</v>
+        <v>20.40058825403925</v>
       </c>
       <c r="O11" t="n">
-        <v>4.505703043583436</v>
+        <v>4.516701036601741</v>
       </c>
       <c r="P11" t="n">
-        <v>391.3574374719107</v>
+        <v>391.2822333206641</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34857,28 +35027,28 @@
         <v>0.0613</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1587740183435577</v>
+        <v>-0.1514821329919254</v>
       </c>
       <c r="J12" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K12" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05884763552202066</v>
+        <v>0.05387447855547689</v>
       </c>
       <c r="M12" t="n">
-        <v>3.700198158170662</v>
+        <v>3.71879896710489</v>
       </c>
       <c r="N12" t="n">
-        <v>20.83101626154547</v>
+        <v>20.96158676644556</v>
       </c>
       <c r="O12" t="n">
-        <v>4.564100816321378</v>
+        <v>4.578382549159207</v>
       </c>
       <c r="P12" t="n">
-        <v>388.3445047761469</v>
+        <v>388.2639002266528</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34935,28 +35105,28 @@
         <v>0.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2198745037854309</v>
+        <v>-0.2139544211957529</v>
       </c>
       <c r="J13" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K13" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06265972094452388</v>
+        <v>0.05996139791750821</v>
       </c>
       <c r="M13" t="n">
-        <v>4.815197851137508</v>
+        <v>4.822635985935999</v>
       </c>
       <c r="N13" t="n">
-        <v>37.36622576609334</v>
+        <v>37.32949571147255</v>
       </c>
       <c r="O13" t="n">
-        <v>6.112791977983002</v>
+        <v>6.109786879382336</v>
       </c>
       <c r="P13" t="n">
-        <v>389.6805552039689</v>
+        <v>389.615106592136</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35013,28 +35183,28 @@
         <v>0.0322</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1840050135036058</v>
+        <v>-0.1770408819597606</v>
       </c>
       <c r="J14" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K14" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04093295496294591</v>
+        <v>0.03825134239141681</v>
       </c>
       <c r="M14" t="n">
-        <v>5.029136091391009</v>
+        <v>5.031053235306342</v>
       </c>
       <c r="N14" t="n">
-        <v>40.98791703218187</v>
+        <v>40.99186620888091</v>
       </c>
       <c r="O14" t="n">
-        <v>6.402180646637665</v>
+        <v>6.402489063550278</v>
       </c>
       <c r="P14" t="n">
-        <v>387.2290164532989</v>
+        <v>387.1520287363299</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35091,28 +35261,28 @@
         <v>0.0313</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.226064621282522</v>
+        <v>-0.2186288604212454</v>
       </c>
       <c r="J15" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K15" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06016685002197675</v>
+        <v>0.056810962024749</v>
       </c>
       <c r="M15" t="n">
-        <v>5.00844792743219</v>
+        <v>5.011213961761841</v>
       </c>
       <c r="N15" t="n">
-        <v>41.24576400526969</v>
+        <v>41.27786600995938</v>
       </c>
       <c r="O15" t="n">
-        <v>6.422286509123499</v>
+        <v>6.424785289016231</v>
       </c>
       <c r="P15" t="n">
-        <v>380.2877733820239</v>
+        <v>380.2055691856888</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35169,28 +35339,28 @@
         <v>0.0407</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1710386177497202</v>
+        <v>-0.1658203118387619</v>
       </c>
       <c r="J16" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K16" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03460771095858861</v>
+        <v>0.03288205326610838</v>
       </c>
       <c r="M16" t="n">
-        <v>5.068753006396443</v>
+        <v>5.063889490246487</v>
       </c>
       <c r="N16" t="n">
-        <v>42.20940983646947</v>
+        <v>42.1129611294871</v>
       </c>
       <c r="O16" t="n">
-        <v>6.496876929453833</v>
+        <v>6.489449986669679</v>
       </c>
       <c r="P16" t="n">
-        <v>375.8514448694798</v>
+        <v>375.7938224995511</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35247,28 +35417,28 @@
         <v>0.0407</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.149819006047163</v>
+        <v>-0.1479177999171227</v>
       </c>
       <c r="J17" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K17" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02682560802613043</v>
+        <v>0.02645947057599907</v>
       </c>
       <c r="M17" t="n">
-        <v>5.041968763808135</v>
+        <v>5.024917337996251</v>
       </c>
       <c r="N17" t="n">
-        <v>42.07223526751368</v>
+        <v>41.87447905733613</v>
       </c>
       <c r="O17" t="n">
-        <v>6.486311376083767</v>
+        <v>6.471049301105357</v>
       </c>
       <c r="P17" t="n">
-        <v>369.8475776686064</v>
+        <v>369.8265627043732</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35325,28 +35495,28 @@
         <v>0.0417</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1330889318724332</v>
+        <v>-0.1301291043403092</v>
       </c>
       <c r="J18" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K18" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03289349079761983</v>
+        <v>0.03180980143568468</v>
       </c>
       <c r="M18" t="n">
-        <v>4.159855472597812</v>
+        <v>4.152520148468724</v>
       </c>
       <c r="N18" t="n">
-        <v>26.90722347974514</v>
+        <v>26.80922494063752</v>
       </c>
       <c r="O18" t="n">
-        <v>5.187217315646718</v>
+        <v>5.177762541932327</v>
       </c>
       <c r="P18" t="n">
-        <v>364.9442248263753</v>
+        <v>364.9115067421902</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35403,28 +35573,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1503334374927842</v>
+        <v>-0.1474228833246713</v>
       </c>
       <c r="J19" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K19" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03344662938181819</v>
+        <v>0.0325408046745076</v>
       </c>
       <c r="M19" t="n">
-        <v>4.525627925715952</v>
+        <v>4.51527392428852</v>
       </c>
       <c r="N19" t="n">
-        <v>33.74468072058283</v>
+        <v>33.61010153412455</v>
       </c>
       <c r="O19" t="n">
-        <v>5.809017190591092</v>
+        <v>5.797421973094985</v>
       </c>
       <c r="P19" t="n">
-        <v>366.7888777784702</v>
+        <v>366.7566997447532</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35481,28 +35651,28 @@
         <v>0.0363</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1479187994706192</v>
+        <v>-0.144106503539452</v>
       </c>
       <c r="J20" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K20" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02869603561537359</v>
+        <v>0.02754546325007035</v>
       </c>
       <c r="M20" t="n">
-        <v>5.003631889212422</v>
+        <v>4.996611068505678</v>
       </c>
       <c r="N20" t="n">
-        <v>38.26490776207776</v>
+        <v>38.13484995704633</v>
       </c>
       <c r="O20" t="n">
-        <v>6.185863542148159</v>
+        <v>6.175342092309246</v>
       </c>
       <c r="P20" t="n">
-        <v>373.4439104360303</v>
+        <v>373.4017693110665</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35559,28 +35729,28 @@
         <v>0.0421</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1322683846759102</v>
+        <v>-0.1313506365421733</v>
       </c>
       <c r="J21" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K21" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02787588833896426</v>
+        <v>0.02781429285903281</v>
       </c>
       <c r="M21" t="n">
-        <v>4.460024997445378</v>
+        <v>4.442174542964005</v>
       </c>
       <c r="N21" t="n">
-        <v>31.52287093441268</v>
+        <v>31.36759530282628</v>
       </c>
       <c r="O21" t="n">
-        <v>5.614523215234993</v>
+        <v>5.600678110981408</v>
       </c>
       <c r="P21" t="n">
-        <v>366.3761482855063</v>
+        <v>366.3660078368118</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35637,28 +35807,28 @@
         <v>0.0345</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1148951154588624</v>
+        <v>-0.1136039229507787</v>
       </c>
       <c r="J22" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K22" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02204667309547792</v>
+        <v>0.0218088599635623</v>
       </c>
       <c r="M22" t="n">
-        <v>4.364116732832438</v>
+        <v>4.347856275441122</v>
       </c>
       <c r="N22" t="n">
-        <v>30.25511884193119</v>
+        <v>30.11016060776876</v>
       </c>
       <c r="O22" t="n">
-        <v>5.50046532958178</v>
+        <v>5.487272601918804</v>
       </c>
       <c r="P22" t="n">
-        <v>365.9983209913091</v>
+        <v>365.9840524896825</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35696,7 +35866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W392"/>
+  <dimension ref="A1:W394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81559,6 +81729,240 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-37.61810791741614,177.9440626164489</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-37.61803757559936,177.94497593509215</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-37.6179127906586,177.9458676027769</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-37.61760461737209,177.9466863334889</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-37.617281011896175,177.94749892507087</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-37.61697812200528,177.94828080697658</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-37.616728680583094,177.94898157614975</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-37.61646878649415,177.94975064136958</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-37.61615762149005,177.95057357008477</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-37.61582746935005,177.95137934407697</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-37.615438901616876,177.9521323335347</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-37.61507592038507,177.95287793843974</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>-37.61462779427337,177.95351845693034</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>-37.61416773968354,177.95419570363802</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>-37.613686362790446,177.95485544146328</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>-37.613197815387586,177.95550553709222</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>-37.61264885667477,177.95607526479222</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>-37.61207561721147,177.95660590940204</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>-37.6114737172438,177.95704735669557</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>-37.610864192431,177.9574939926416</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>-37.61020855156181,177.95784281268973</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:53:09+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-37.618094028205135,177.944057092686</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-37.618026344233236,177.94497146826126</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-37.61789881579181,177.94586204471645</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-37.617590213863,177.94668060486921</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-37.617274067363645,177.94749616302664</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-37.616968520688154,177.94827629122977</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-37.616717425920086,177.94897352578798</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-37.616460170466034,177.94974285568043</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-37.61615572305253,177.95057185458853</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-37.615827396333586,177.95137927809617</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-37.615451460398006,177.95214368224362</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-37.61507481492452,177.95287678080444</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>-37.614630533537884,177.95352204597708</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>-37.614167441495525,177.95419528061868</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>-37.6136850327294,177.954853450471</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>-37.61320125247583,177.95551133969215</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-37.61265229928942,177.95608148019053</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>-37.612074399878644,177.9566036692748</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>-37.611477495610416,177.95705648085567</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>-37.610867669837134,177.95750526992506</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>-37.61021232144139,177.95785503842652</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
